--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Comentarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen_Posts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stats_Plataforma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="URLs_Fallidas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats_Extraccion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,7 +1325,7 @@
       <c r="H20" s="1" t="n">
         <v>46211.58980324074</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="1" t="n">
         <v>46211</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -1388,7 +1392,7 @@
       <c r="H21" s="1" t="n">
         <v>46210.59957175926</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I21" s="1" t="n">
         <v>46210</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -1526,23 +1530,23 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Traigan de vuelta a los pokemones</t>
+          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-21T21:29:07.000Z</t>
+          <t>2026-07-23T09:14:50.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46224.8952199074</v>
+        <v>46226.38530092593</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21:29:07</t>
+          <t>09:14:50</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1561,7 +1565,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
         </is>
       </c>
     </row>
@@ -1587,28 +1591,28 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pero si se parese auna  caca</t>
+          <t>Jajaja</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-17T23:25:08.000Z</t>
+          <t>2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46220.97578703704</v>
+        <v>46225.96142361111</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23:25:08</t>
+          <t>23:04:27</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1622,13 +1626,13 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1637,40 +1641,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Traigan de vuelta a los pokemones</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46223.08563657408</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>46223</v>
+        <v>46224.8952199074</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>46224</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>02:03:19</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>21:29:07</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1683,13 +1685,13 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1698,40 +1700,38 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Pero si se parese auna  caca</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46217.89942129629</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>46217</v>
+        <v>46220.97578703704</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>46220</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21:35:10</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>23:25:08</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1744,13 +1744,13 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1759,22 +1759,40 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tomé factores de tranferencia para los dolores</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-21T23:29:38.000Z</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>46224.97891203704</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>23:29:38</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1784,16 +1802,16 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1802,20 +1820,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vdkdroq</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>46223.08563657408</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>02:03:19</t>
+        </is>
+      </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
@@ -1827,16 +1861,16 @@
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1845,40 +1879,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-18T01:02:17.000Z</t>
+          <t>2026-07-14T21:35:10.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>46221</v>
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>46217</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>21:35:10</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1891,13 +1923,13 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1906,40 +1938,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1949,16 +1963,16 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1967,40 +1981,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-07-18T00:09:32.000Z</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>46221.00662037037</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>00:09:32</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2010,16 +2006,16 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2028,40 +2024,38 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>46219</v>
+        <v>46221.04325231481</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>46221</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>01:37:23</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>01:02:17</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2074,13 +2068,13 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2089,20 +2083,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>La basura que con sumen los aguebados jajaja</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>02:24:12</t>
+        </is>
+      </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
@@ -2114,16 +2124,16 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2132,20 +2142,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>46221.00662037037</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>00:09:32</t>
+        </is>
+      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -2157,16 +2183,16 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2175,20 +2201,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
@@ -2200,16 +2242,16 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2218,12 +2260,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2252,7 +2294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2261,12 +2303,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2295,7 +2337,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2304,12 +2346,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2338,21 +2380,21 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2381,21 +2423,21 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2424,21 +2466,21 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2467,7 +2509,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2476,12 +2518,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2510,7 +2552,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2519,12 +2561,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2553,7 +2595,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2562,12 +2604,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2596,7 +2638,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2605,12 +2647,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2639,7 +2681,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2648,12 +2690,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2682,7 +2724,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2691,12 +2733,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2725,7 +2767,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2734,12 +2776,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2768,7 +2810,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2777,12 +2819,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2811,7 +2853,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2820,12 +2862,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2852,6 +2894,1849 @@
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>42</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>43</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>44</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>post_number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>post_url</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Total_Comentarios</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total_Likes</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Primera_Extraccion</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ultima_Extraccion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/3261599530668110/</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5yxYgAy5c/</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46210.59957175926</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>46211.58980324074</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>46220.97578703704</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>46226.38530092593</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>46224.97891203704</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>46221.04325231481</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>46221.04325231481</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Total_Posts</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Total_Comentarios</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Promedio_Likes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total_Likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/3261599530668110/</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>total_attempts</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>successful</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>no_comments</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>invalid_comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,23 +1530,23 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
+          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-23T09:14:50.000Z</t>
+          <t>2026-07-23T20:58:28.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46226.38530092593</v>
+        <v>46226.87393518518</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>09:14:50</t>
+          <t>20:58:28</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1565,7 +1565,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
         </is>
       </c>
     </row>
@@ -1591,29 +1591,27 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jajaja</t>
+          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-22T23:04:27.000Z</t>
+          <t>2026-07-23T09:14:50.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46225.96142361111</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>46225</v>
+        <v>46226.38530092593</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>46226</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23:04:27</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>09:14:50</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1626,7 +1624,7 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
         </is>
       </c>
     </row>
@@ -1652,23 +1650,23 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Traigan de vuelta a los pokemones</t>
+          <t>Jajaja</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-21T21:29:07.000Z</t>
+          <t>2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46224.8952199074</v>
+        <v>46225.96142361111</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21:29:07</t>
+          <t>23:04:27</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1685,7 +1683,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
     </row>
@@ -1711,27 +1709,27 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pero si se parese auna  caca</t>
+          <t>Traigan de vuelta a los pokemones</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-17T23:25:08.000Z</t>
+          <t>2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46220.97578703704</v>
+        <v>46224.8952199074</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23:25:08</t>
+          <t>21:29:07</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1744,13 +1742,13 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1759,40 +1757,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>Pero si se parese auna  caca</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46224.97891203704</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>46224</v>
+        <v>46220.97578703704</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>46220</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23:29:38</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>23:25:08</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1805,7 +1801,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
     </row>
@@ -1831,27 +1827,29 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46223.08563657408</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>46223</v>
+        <v>46227.10761574074</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>46227</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>02:03:19</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+          <t>02:34:58</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1864,7 +1862,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -1890,23 +1888,23 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1923,13 +1921,13 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1938,20 +1936,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vdkdroq</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>46223.08563657408</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>02:03:19</t>
+        </is>
+      </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
@@ -1963,16 +1977,16 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1981,20 +1995,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
@@ -2006,16 +2036,16 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2024,36 +2054,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -2065,16 +2079,16 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2083,36 +2097,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I34" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
         <v>0</v>
       </c>
@@ -2124,16 +2122,16 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2142,34 +2140,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I35" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2186,7 +2184,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
@@ -2212,23 +2210,23 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>La basura que con sumen los aguebados jajaja</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46221.10013888889</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>02:24:12</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2245,13 +2243,13 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2260,20 +2258,36 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>46221.00662037037</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>00:09:32</t>
+        </is>
+      </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -2285,16 +2299,16 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2303,20 +2317,36 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
@@ -2328,16 +2358,16 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2346,12 +2376,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2380,7 +2410,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2389,12 +2419,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2423,7 +2453,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2432,12 +2462,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2466,7 +2496,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2475,22 +2505,40 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2500,40 +2548,58 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2543,30 +2609,30 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2595,21 +2661,21 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2638,21 +2704,21 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2681,7 +2747,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2690,12 +2756,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2724,7 +2790,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2733,12 +2799,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2767,7 +2833,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2776,12 +2842,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2810,7 +2876,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2819,12 +2885,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2853,7 +2919,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2862,12 +2928,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2896,7 +2962,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2905,12 +2971,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2939,7 +3005,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2948,12 +3014,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2982,7 +3048,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2991,12 +3057,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3022,6 +3088,178 @@
         </is>
       </c>
       <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>41</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>42</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>43</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>44</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3553,7 +3791,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -3562,7 +3800,7 @@
         <v>46220.97578703704</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46226.38530092593</v>
+        <v>46226.87393518518</v>
       </c>
     </row>
     <row r="23">
@@ -3580,7 +3818,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -3589,7 +3827,7 @@
         <v>46217.89942129629</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
     </row>
     <row r="24">
@@ -3776,13 +4014,17 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4154,13 +4396,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -4196,7 +4438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4394,7 +4636,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4406,7 +4648,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4418,7 +4660,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4430,7 +4672,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4442,7 +4684,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4454,7 +4696,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4466,7 +4708,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4478,7 +4720,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4490,7 +4732,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4502,7 +4744,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4514,7 +4756,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4526,7 +4768,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4538,7 +4780,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4550,7 +4792,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4562,7 +4804,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4574,7 +4816,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4586,7 +4828,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4598,7 +4840,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4610,7 +4852,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4622,7 +4864,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4634,7 +4876,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4646,7 +4888,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4658,22 +4900,10 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
         <is>
           <t>FAILED_ALL_ATTEMPTS</t>
         </is>
@@ -4725,16 +4955,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,23 +1530,23 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
+          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:28.000Z</t>
+          <t>2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46226.87393518518</v>
+        <v>46228.08181712963</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20:58:28</t>
+          <t>01:57:49</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1565,7 +1565,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
     </row>
@@ -1591,23 +1591,23 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
+          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-23T09:14:50.000Z</t>
+          <t>2026-07-23T20:58:28.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46226.38530092593</v>
+        <v>46226.87393518518</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>46226</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>09:14:50</t>
+          <t>20:58:28</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1624,7 +1624,7 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
         </is>
       </c>
     </row>
@@ -1650,23 +1650,23 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jajaja</t>
+          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-22T23:04:27.000Z</t>
+          <t>2026-07-23T09:14:50.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46225.96142361111</v>
+        <v>46226.38530092593</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>23:04:27</t>
+          <t>09:14:50</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1683,7 +1683,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
         </is>
       </c>
     </row>
@@ -1709,23 +1709,23 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Traigan de vuelta a los pokemones</t>
+          <t>Jajaja</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-21T21:29:07.000Z</t>
+          <t>2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46224.8952199074</v>
+        <v>46225.96142361111</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21:29:07</t>
+          <t>23:04:27</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1742,7 +1742,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
     </row>
@@ -1768,27 +1768,27 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pero si se parese auna  caca</t>
+          <t>Traigan de vuelta a los pokemones</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-17T23:25:08.000Z</t>
+          <t>2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46220.97578703704</v>
+        <v>46224.8952199074</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23:25:08</t>
+          <t>21:29:07</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1801,13 +1801,13 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1816,40 +1816,38 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>Pero si se parese auna  caca</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46227.10761574074</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>46227</v>
+        <v>46220.97578703704</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>46220</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>02:34:58</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>23:25:08</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1862,7 +1860,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
     </row>
@@ -1888,23 +1886,23 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1921,7 +1919,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -1947,23 +1945,23 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -1980,7 +1978,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2006,23 +2004,23 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2039,13 +2037,13 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2054,20 +2052,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -2079,16 +2093,16 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2097,12 +2111,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2131,7 +2145,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2140,36 +2154,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I35" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -2181,16 +2179,16 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2199,34 +2197,34 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46221.10013888889</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I36" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>02:24:12</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2243,7 +2241,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
@@ -2269,23 +2267,23 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>La basura que con sumen los aguebados jajaja</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.10013888889</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>02:24:12</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2302,7 +2300,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
     </row>
@@ -2328,23 +2326,23 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2361,13 +2359,13 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2376,20 +2374,36 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
@@ -2401,16 +2415,16 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2419,12 +2433,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2453,7 +2467,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2462,12 +2476,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2496,7 +2510,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2505,40 +2519,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-07-24T07:43:32.000Z</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="n">
-        <v>46227.32189814815</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>46227</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>07:43:32</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2548,12 +2544,12 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2577,29 +2573,27 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Por que los nuevos se parecen a la 💩</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-07-24T07:43:32.000Z</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>46226</v>
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>46227</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22:50:34</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>07:43:32</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2612,7 +2606,7 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
         </is>
       </c>
     </row>
@@ -2636,11 +2630,27 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
@@ -2652,16 +2662,16 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2670,12 +2680,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2704,7 +2714,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2713,12 +2723,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2747,21 +2757,21 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2790,7 +2800,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2799,12 +2809,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2833,7 +2843,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2842,12 +2852,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2876,7 +2886,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2885,12 +2895,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2919,7 +2929,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2928,12 +2938,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2962,7 +2972,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2971,12 +2981,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3005,7 +3015,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3014,12 +3024,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3048,7 +3058,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3057,12 +3067,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3091,7 +3101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3100,12 +3110,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3134,7 +3144,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3143,12 +3153,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3177,7 +3187,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3186,12 +3196,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3220,7 +3230,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3229,12 +3239,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3260,6 +3270,49 @@
         </is>
       </c>
       <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>44</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3791,7 +3844,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -3800,7 +3853,7 @@
         <v>46220.97578703704</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46226.87393518518</v>
+        <v>46228.08181712963</v>
       </c>
     </row>
     <row r="23">
@@ -4399,10 +4452,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       <c r="H24" s="1" t="n">
         <v>46228.08181712963</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>46228</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1549,10 +1549,8 @@
           <t>01:57:49</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1886,27 +1884,29 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46227.10761574074</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>46227</v>
+        <v>46228.78229166667</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>46228</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>02:34:58</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+          <t>18:46:30</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -1945,23 +1945,23 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -1978,7 +1978,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2004,23 +2004,23 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2037,7 +2037,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2063,23 +2063,23 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2096,13 +2096,13 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2111,20 +2111,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I34" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
@@ -2136,16 +2152,16 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2154,12 +2170,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2188,7 +2204,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2197,36 +2213,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I36" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
         <v>0</v>
       </c>
@@ -2238,16 +2238,16 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2256,34 +2256,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46221.10013888889</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>02:24:12</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2300,7 +2300,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
@@ -2326,23 +2326,23 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>La basura que con sumen los aguebados jajaja</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.10013888889</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>02:24:12</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2359,7 +2359,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
     </row>
@@ -2385,23 +2385,23 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2418,13 +2418,13 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2433,20 +2433,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
@@ -2458,16 +2474,16 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2476,12 +2492,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2510,7 +2526,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2519,12 +2535,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2553,7 +2569,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2562,36 +2578,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-07-24T07:43:32.000Z</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>46227.32189814815</v>
-      </c>
-      <c r="I43" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>07:43:32</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2632,23 +2632,23 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Por que los nuevos se parecen a la 💩</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-07-24T07:43:32.000Z</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46227.32189814815</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>07:43:32</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2665,7 +2665,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
         </is>
       </c>
     </row>
@@ -2689,11 +2689,27 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
@@ -2705,16 +2721,16 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2723,12 +2739,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2757,7 +2773,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2766,12 +2782,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2800,21 +2816,21 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2843,7 +2859,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2852,12 +2868,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2886,7 +2902,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2895,12 +2911,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2929,7 +2945,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2938,12 +2954,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2972,7 +2988,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2981,12 +2997,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3015,7 +3031,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3024,12 +3040,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3058,7 +3074,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3067,12 +3083,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3101,7 +3117,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3110,12 +3126,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3144,7 +3160,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3153,12 +3169,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3187,7 +3203,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3196,12 +3212,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3230,7 +3246,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3239,20 +3255,40 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
@@ -3263,17 +3299,21 @@
         <v>0</v>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3282,12 +3322,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3313,6 +3353,92 @@
         </is>
       </c>
       <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>43</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>44</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3871,7 +3997,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -3880,7 +4006,7 @@
         <v>46217.89942129629</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46228.78229166667</v>
       </c>
     </row>
     <row r="24">
@@ -4347,13 +4473,17 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4452,7 +4582,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>0.06</v>
@@ -4468,10 +4598,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -4809,7 +4939,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+          <t>https://www.instagram.com/p/DZ5yxYgAy5c/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4821,7 +4951,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4833,7 +4963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4845,7 +4975,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4857,7 +4987,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4869,7 +4999,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4881,7 +5011,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4893,7 +5023,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4905,7 +5035,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4917,7 +5047,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4929,7 +5059,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5017,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,27 +1530,29 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
+          <t>Se quedaron sin ideas  que colección más horrible</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-25T01:57:49.000Z</t>
+          <t>2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46228.08181712963</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>46228</v>
+        <v>46230.54899305556</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>46230</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>01:57:49</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+          <t>13:10:33</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1563,7 +1565,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qjQJPjSo79PmXE9EfckDcND6djP8YXbaGA6vVCzdkmAijk99o4wyN2EfEBBD6dyAl?comment_id=2090210734944742', 'commentId': '2090210734944742', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzIwOTAyMTA3MzQ5NDQ3NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yMDkwMjEwNzM0OTQ0NzQy', 'date': '2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
     </row>
@@ -1589,23 +1591,23 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
+          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:28.000Z</t>
+          <t>2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46226.87393518518</v>
+        <v>46228.08181712963</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20:58:28</t>
+          <t>01:57:49</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1622,7 +1624,7 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
     </row>
@@ -1648,23 +1650,23 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
+          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-23T09:14:50.000Z</t>
+          <t>2026-07-23T20:58:28.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46226.38530092593</v>
+        <v>46226.87393518518</v>
       </c>
       <c r="I26" s="1" t="n">
         <v>46226</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>09:14:50</t>
+          <t>20:58:28</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1681,7 +1683,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
         </is>
       </c>
     </row>
@@ -1707,23 +1709,23 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jajaja</t>
+          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-22T23:04:27.000Z</t>
+          <t>2026-07-23T09:14:50.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46225.96142361111</v>
+        <v>46226.38530092593</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>23:04:27</t>
+          <t>09:14:50</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1740,7 +1742,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
         </is>
       </c>
     </row>
@@ -1766,23 +1768,23 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Traigan de vuelta a los pokemones</t>
+          <t>Jajaja</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-21T21:29:07.000Z</t>
+          <t>2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46224.8952199074</v>
+        <v>46225.96142361111</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21:29:07</t>
+          <t>23:04:27</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1799,7 +1801,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
     </row>
@@ -1825,27 +1827,27 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pero si se parese auna  caca</t>
+          <t>Traigan de vuelta a los pokemones</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-17T23:25:08.000Z</t>
+          <t>2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46220.97578703704</v>
+        <v>46224.8952199074</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23:25:08</t>
+          <t>21:29:07</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1858,13 +1860,13 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1873,40 +1875,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>Pero si se parese auna  caca</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46228.78229166667</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>46228</v>
+        <v>46220.97578703704</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>46220</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18:46:30</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>23:25:08</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
     </row>
@@ -1945,23 +1945,23 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46228.78229166667</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>02:34:58</t>
+          <t>18:46:30</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -1978,7 +1978,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -2004,23 +2004,23 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2037,7 +2037,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2063,23 +2063,23 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2096,7 +2096,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2122,23 +2122,23 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2155,13 +2155,13 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2170,20 +2170,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -2195,16 +2211,16 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2213,12 +2229,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2247,7 +2263,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2256,36 +2272,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I37" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -2297,16 +2297,16 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2315,34 +2315,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46221.10013888889</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>02:24:12</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2359,7 +2359,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
@@ -2385,23 +2385,23 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>La basura que con sumen los aguebados jajaja</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.10013888889</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>02:24:12</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2418,7 +2418,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
     </row>
@@ -2444,23 +2444,23 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2477,13 +2477,13 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2492,20 +2492,36 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
@@ -2517,16 +2533,16 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2535,12 +2551,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2569,7 +2585,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2578,12 +2594,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2612,7 +2628,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2621,36 +2637,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-07-24T07:43:32.000Z</t>
-        </is>
-      </c>
-      <c r="H44" s="1" t="n">
-        <v>46227.32189814815</v>
-      </c>
-      <c r="I44" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>07:43:32</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>0</v>
       </c>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2691,23 +2691,23 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Por que los nuevos se parecen a la 💩</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-07-24T07:43:32.000Z</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46227.32189814815</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>07:43:32</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2724,7 +2724,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,27 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
@@ -2764,16 +2780,16 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2782,12 +2798,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2816,7 +2832,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2825,12 +2841,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2859,21 +2875,21 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2902,7 +2918,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2911,12 +2927,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2945,7 +2961,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2954,12 +2970,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2988,7 +3004,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2997,12 +3013,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3031,7 +3047,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3040,12 +3056,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3074,7 +3090,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3083,12 +3099,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3117,7 +3133,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3126,12 +3142,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3160,7 +3176,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3169,12 +3185,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3203,7 +3219,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3212,12 +3228,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3246,7 +3262,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3255,40 +3271,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
         <v>0</v>
       </c>
@@ -3299,17 +3295,13 @@
         <v>0</v>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3330,12 +3322,32 @@
           <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
@@ -3346,17 +3358,21 @@
         <v>0</v>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3365,12 +3381,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3399,7 +3415,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3408,12 +3424,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3439,6 +3455,49 @@
         </is>
       </c>
       <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>44</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3970,7 +4029,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -3979,7 +4038,7 @@
         <v>46220.97578703704</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46228.08181712963</v>
+        <v>46230.54899305556</v>
       </c>
     </row>
     <row r="23">
@@ -4582,7 +4641,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
         <v>0.06</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       <c r="H24" s="1" t="n">
         <v>46230.54899305556</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>46230</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1549,10 +1549,8 @@
           <t>13:10:33</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1945,27 +1943,29 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-07-28T07:15:20.000Z</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46228.78229166667</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>46228</v>
+        <v>46231.30231481481</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>46231</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18:46:30</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+          <t>07:15:20</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2004,23 +2004,23 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46228.78229166667</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>02:34:58</t>
+          <t>18:46:30</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2037,7 +2037,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -2063,23 +2063,23 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2096,7 +2096,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2122,23 +2122,23 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2155,7 +2155,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2181,23 +2181,23 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2214,13 +2214,13 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2229,20 +2229,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
@@ -2254,16 +2270,16 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2272,12 +2288,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2306,7 +2322,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2315,36 +2331,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H38" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I38" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
         <v>0</v>
       </c>
@@ -2356,16 +2356,16 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2374,34 +2374,34 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46221.10013888889</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I39" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>02:24:12</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2418,7 +2418,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
@@ -2444,23 +2444,23 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>La basura que con sumen los aguebados jajaja</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.10013888889</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>02:24:12</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2477,7 +2477,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
     </row>
@@ -2503,23 +2503,23 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2536,13 +2536,13 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2551,20 +2551,36 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
@@ -2576,16 +2592,16 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2594,12 +2610,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2628,7 +2644,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2637,12 +2653,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2671,7 +2687,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2680,36 +2696,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-07-24T07:43:32.000Z</t>
-        </is>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>46227.32189814815</v>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>07:43:32</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
         <v>0</v>
       </c>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
-        </is>
-      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2750,23 +2750,23 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Por que los nuevos se parecen a la 💩</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-07-24T07:43:32.000Z</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46227.32189814815</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>07:43:32</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2783,7 +2783,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
         </is>
       </c>
     </row>
@@ -2807,11 +2807,27 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -2823,16 +2839,16 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2841,12 +2857,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2875,7 +2891,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2884,12 +2900,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2918,21 +2934,21 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2961,7 +2977,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2970,12 +2986,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3004,7 +3020,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3013,12 +3029,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3047,7 +3063,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3056,12 +3072,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3090,7 +3106,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3099,12 +3115,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3133,7 +3149,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3142,12 +3158,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3176,7 +3192,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3185,12 +3201,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3219,7 +3235,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3228,12 +3244,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3262,7 +3278,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3271,12 +3287,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3305,7 +3321,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3314,40 +3330,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H59" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>0</v>
       </c>
@@ -3358,17 +3354,13 @@
         <v>0</v>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3389,12 +3381,32 @@
           <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
@@ -3405,17 +3417,21 @@
         <v>0</v>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3424,12 +3440,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3458,7 +3474,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3467,12 +3483,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3498,6 +3514,49 @@
         </is>
       </c>
       <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>44</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4056,7 +4115,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4065,7 +4124,7 @@
         <v>46217.89942129629</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46228.78229166667</v>
+        <v>46231.30231481481</v>
       </c>
     </row>
     <row r="24">
@@ -4641,10 +4700,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -4680,7 +4739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4998,7 +5057,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5yxYgAy5c/</t>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5010,7 +5069,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5022,7 +5081,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5034,7 +5093,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5046,7 +5105,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5058,7 +5117,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5070,7 +5129,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5082,7 +5141,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5094,7 +5153,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5106,7 +5165,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5118,7 +5177,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5130,22 +5189,10 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
         <is>
           <t>FAILED_ALL_ATTEMPTS</t>
         </is>
@@ -5197,16 +5244,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1954,7 +1954,7 @@
       <c r="H31" s="1" t="n">
         <v>46231.30231481481</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="I31" s="1" t="n">
         <v>46231</v>
       </c>
       <c r="J31" t="inlineStr">
@@ -1962,10 +1962,8 @@
           <t>07:15:20</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K31" t="n">
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2385,27 +2383,31 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
+          <t>Yo creo que el encargado no se hizo entender.
+Empleado: Que colección de Mochis sacamos ahora!
+Jefe: Cualquier mierda.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-18T01:02:17.000Z</t>
+          <t>2026-07-28T21:56:33.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I39" s="1" t="n">
-        <v>46221</v>
+        <v>46231.91427083333</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>46231</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+          <t>21:56:33</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2418,13 +2420,13 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2433,34 +2435,34 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46221.10013888889</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I40" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>02:24:12</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2477,7 +2479,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
@@ -2503,23 +2505,23 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>La basura que con sumen los aguebados jajaja</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.10013888889</v>
       </c>
       <c r="I41" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>02:24:12</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2536,7 +2538,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
     </row>
@@ -2562,23 +2564,23 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2595,13 +2597,13 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2610,20 +2612,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -2635,16 +2653,16 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2653,12 +2671,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2687,7 +2705,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2696,12 +2714,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2730,7 +2748,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2739,36 +2757,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-07-24T07:43:32.000Z</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="n">
-        <v>46227.32189814815</v>
-      </c>
-      <c r="I46" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>07:43:32</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
         <v>0</v>
       </c>
@@ -2780,12 +2782,12 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2809,23 +2811,23 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Por que los nuevos se parecen a la 💩</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-07-24T07:43:32.000Z</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46227.32189814815</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>07:43:32</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2842,7 +2844,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
         </is>
       </c>
     </row>
@@ -2866,11 +2868,27 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
@@ -2882,16 +2900,16 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2900,12 +2918,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2934,7 +2952,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2943,12 +2961,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2977,21 +2995,21 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3020,7 +3038,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3029,12 +3047,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3063,7 +3081,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3072,12 +3090,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3106,7 +3124,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3115,12 +3133,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3149,7 +3167,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3158,12 +3176,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3192,7 +3210,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3201,12 +3219,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3235,7 +3253,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3244,12 +3262,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3278,7 +3296,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3287,12 +3305,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3321,7 +3339,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3330,12 +3348,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3364,7 +3382,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3373,40 +3391,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H60" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I60" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
         <v>0</v>
       </c>
@@ -3417,17 +3415,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3448,12 +3442,32 @@
           <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
@@ -3464,17 +3478,21 @@
         <v>0</v>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3483,12 +3501,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3517,7 +3535,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3526,12 +3544,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3557,6 +3575,49 @@
         </is>
       </c>
       <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>44</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4188,16 +4249,16 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
         <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>46221.04325231481</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46221.04325231481</v>
+        <v>46231.91427083333</v>
       </c>
     </row>
     <row r="27">
@@ -4700,13 +4761,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2396,7 +2396,7 @@
       <c r="H39" s="1" t="n">
         <v>46231.91427083333</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="I39" s="1" t="n">
         <v>46231</v>
       </c>
       <c r="J39" t="inlineStr">
@@ -2404,10 +2404,8 @@
           <t>21:56:33</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K39" t="n">
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2766,13 +2764,31 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>20:28:55</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2782,16 +2798,16 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2800,36 +2816,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-07-24T07:43:32.000Z</t>
-        </is>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>46227.32189814815</v>
-      </c>
-      <c r="I47" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>07:43:32</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2870,23 +2870,23 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Por que los nuevos se parecen a la 💩</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-07-24T07:43:32.000Z</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46227.32189814815</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>07:43:32</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -2903,7 +2903,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,27 @@
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -2943,16 +2959,16 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2961,12 +2977,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2995,7 +3011,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3004,12 +3020,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3038,21 +3054,21 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3081,7 +3097,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3090,12 +3106,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3124,7 +3140,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3133,12 +3149,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3167,7 +3183,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3176,12 +3192,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3210,7 +3226,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3219,12 +3235,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3253,7 +3269,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3262,12 +3278,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3296,7 +3312,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3305,12 +3321,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3339,7 +3355,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3348,12 +3364,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3382,7 +3398,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3391,12 +3407,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3425,7 +3441,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3434,40 +3450,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
         <v>0</v>
       </c>
@@ -3478,17 +3474,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3509,12 +3501,32 @@
           <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
@@ -3525,17 +3537,21 @@
         <v>0</v>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3544,12 +3560,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3578,7 +3594,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3587,12 +3603,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3618,6 +3634,49 @@
         </is>
       </c>
       <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>44</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4349,13 +4408,17 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4758,10 +4821,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
         <v>0.1</v>
@@ -4800,7 +4863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4986,7 +5049,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4998,7 +5061,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5010,7 +5073,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5022,7 +5085,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5034,7 +5097,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5046,7 +5109,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5058,7 +5121,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5070,7 +5133,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5082,7 +5145,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5094,7 +5157,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5106,7 +5169,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5118,7 +5181,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5130,7 +5193,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5142,7 +5205,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5154,7 +5217,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5166,7 +5229,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5178,7 +5241,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5190,7 +5253,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5202,7 +5265,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5214,7 +5277,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5226,7 +5289,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5238,22 +5301,10 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
         <is>
           <t>FAILED_ALL_ATTEMPTS</t>
         </is>
@@ -5305,16 +5356,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -20,11 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -55,10 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2777,7 +2774,7 @@
       <c r="H46" s="1" t="n">
         <v>46232.85341435186</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I46" s="1" t="n">
         <v>46232</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -2785,10 +2782,8 @@
           <t>20:28:55</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K46" t="n">
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1920,7 +1920,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1929,36 +1929,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-07-28T07:15:20.000Z</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>46231.30231481481</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>07:15:20</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
         <v>0</v>
       </c>
@@ -1970,12 +1954,12 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1999,23 +1983,23 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-07-28T07:15:20.000Z</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46228.78229166667</v>
+        <v>46231.30231481481</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>18:46:30</t>
+          <t>07:15:20</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2032,7 +2016,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2058,23 +2042,23 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46228.78229166667</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>02:34:58</t>
+          <t>18:46:30</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2091,7 +2075,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -2117,23 +2101,23 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2150,7 +2134,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2176,23 +2160,23 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2209,7 +2193,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2235,23 +2219,23 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2268,13 +2252,13 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2283,20 +2267,36 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
@@ -2308,16 +2308,16 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2360,167 +2360,135 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>23</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>24</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>25</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Yo creo que el encargado no se hizo entender.
 Empleado: Que colección de Mochis sacamos ahora!
 Jefe: Cualquier mierda.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>2026-07-28T21:56:33.000Z</t>
         </is>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H41" s="1" t="n">
         <v>46231.91427083333</v>
       </c>
-      <c r="I39" s="1" t="n">
+      <c r="I41" s="1" t="n">
         <v>46231</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>21:56:33</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="K41" t="n">
         <v>1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>25</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I40" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>26</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I41" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2533,13 +2501,13 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2548,34 +2516,34 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2592,13 +2560,13 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2607,36 +2575,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-07-16T01:37:23.000Z</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="I43" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>01:37:23</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -2648,16 +2600,16 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2666,20 +2618,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>La basura que con sumen los aguebados jajaja</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>02:24:12</t>
+        </is>
+      </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
@@ -2691,16 +2659,16 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2709,20 +2677,36 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>46221.00662037037</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>00:09:32</t>
+        </is>
+      </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
@@ -2734,16 +2718,16 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2752,34 +2736,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-29T20:28:55.000Z</t>
+          <t>2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46232.85341435186</v>
+        <v>46219.06762731481</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>46232</v>
+        <v>46219</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>20:28:55</t>
+          <t>01:37:23</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2796,13 +2780,13 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2811,12 +2795,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2845,7 +2829,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2854,36 +2838,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-07-24T07:43:32.000Z</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="n">
-        <v>46227.32189814815</v>
-      </c>
-      <c r="I48" s="1" t="n">
-        <v>46227</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>07:43:32</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
         <v>0</v>
       </c>
@@ -2895,16 +2863,16 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2913,36 +2881,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-07-23T22:50:34.000Z</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>22:50:34</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -2954,16 +2906,16 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2972,20 +2924,36 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>20:28:55</t>
+        </is>
+      </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
@@ -2997,16 +2965,16 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3015,12 +2983,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3049,7 +3017,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3058,20 +3026,36 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
@@ -3083,38 +3067,54 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
@@ -3126,30 +3126,30 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3178,21 +3178,21 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3221,21 +3221,21 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3488,40 +3488,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
         <v>0</v>
       </c>
@@ -3532,21 +3512,17 @@
         <v>0</v>
       </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3555,12 +3531,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3589,7 +3565,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3598,12 +3574,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3632,7 +3608,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3641,12 +3617,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3672,6 +3648,202 @@
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>42</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>42</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>43</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>44</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4858,7 +5030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4996,7 +5168,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5008,7 +5180,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5020,7 +5192,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5032,7 +5204,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5044,7 +5216,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5056,7 +5228,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5068,7 +5240,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5080,7 +5252,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5092,7 +5264,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5104,7 +5276,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5116,7 +5288,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5128,7 +5300,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5140,7 +5312,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5152,7 +5324,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5164,7 +5336,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5176,7 +5348,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5188,7 +5360,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5200,7 +5372,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5212,7 +5384,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5224,7 +5396,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5236,7 +5408,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5248,7 +5420,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5260,7 +5432,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5272,7 +5444,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5284,7 +5456,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5296,10 +5468,82 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>FAILED_ALL_ATTEMPTS</t>
         </is>
@@ -5351,16 +5595,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -20,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -53,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2935,27 +2938,29 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+          <t>Si también yo todo una bb y le yebo debes en cuando</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-29T20:28:55.000Z</t>
+          <t>2026-08-02T03:54:11.000Z</t>
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46232.85341435186</v>
-      </c>
-      <c r="I50" s="1" t="n">
-        <v>46232</v>
+        <v>46236.16262731481</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>46236</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>20:28:55</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+          <t>03:54:11</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2968,7 +2973,7 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
         </is>
       </c>
     </row>
@@ -2992,13 +2997,31 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Alanissofia</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-08-02T00:21:49.000Z</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>46236.01515046296</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>00:21:49</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3008,16 +3031,16 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3026,34 +3049,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-24T07:43:32.000Z</t>
+          <t>2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46232.85341435186</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>20:28:55</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3070,13 +3093,13 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3085,36 +3108,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-07-23T22:50:34.000Z</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>22:50:34</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="n">
         <v>0</v>
       </c>
@@ -3126,12 +3133,12 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3153,11 +3160,27 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
@@ -3169,16 +3192,16 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3187,20 +3210,36 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
@@ -3212,16 +3251,16 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3230,12 +3269,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3264,21 +3303,21 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3307,21 +3346,21 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3350,7 +3389,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3359,12 +3398,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3393,7 +3432,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3402,12 +3441,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3436,7 +3475,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3445,12 +3484,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3479,7 +3518,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3488,12 +3527,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3522,7 +3561,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3531,12 +3570,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3565,7 +3604,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3574,12 +3613,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3608,7 +3647,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3617,12 +3656,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3651,7 +3690,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3660,40 +3699,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H66" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I66" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
         <v>0</v>
       </c>
@@ -3704,21 +3723,17 @@
         <v>0</v>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3727,12 +3742,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3761,7 +3776,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3770,20 +3785,40 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
@@ -3794,17 +3829,21 @@
         <v>0</v>
       </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3813,12 +3852,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3844,6 +3883,92 @@
         </is>
       </c>
       <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>43</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>44</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4575,16 +4700,16 @@
         </is>
       </c>
       <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
         <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>46232.85341435186</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46232.85341435186</v>
+        <v>46236.16262731481</v>
       </c>
     </row>
     <row r="31">
@@ -4991,13 +5116,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5030,7 +5155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5168,7 +5293,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5180,7 +5305,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5192,7 +5317,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5204,7 +5329,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5216,7 +5341,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5228,7 +5353,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5240,7 +5365,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5252,7 +5377,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5264,7 +5389,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5276,7 +5401,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5288,7 +5413,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5300,7 +5425,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5312,7 +5437,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5324,7 +5449,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5336,7 +5461,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5348,7 +5473,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5360,7 +5485,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5372,7 +5497,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5384,7 +5509,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5396,7 +5521,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5408,7 +5533,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5420,7 +5545,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5432,7 +5557,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5444,7 +5569,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5456,7 +5581,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5468,82 +5593,10 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
         <is>
           <t>FAILED_ALL_ATTEMPTS</t>
         </is>
@@ -5595,16 +5648,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,27 +1530,29 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Se quedaron sin ideas  que colección más horrible</t>
+          <t>https://www.facebook.com/share/r/1LkUytha79/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-27T13:10:33.000Z</t>
+          <t>2026-08-03T02:25:19.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46230.54899305556</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>46230</v>
+        <v>46237.10091435185</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>46237</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13:10:33</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+          <t>02:25:19</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1563,7 +1565,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qjQJPjSo79PmXE9EfckDcND6djP8YXbaGA6vVCzdkmAijk99o4wyN2EfEBBD6dyAl?comment_id=2090210734944742', 'commentId': '2090210734944742', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzIwOTAyMTA3MzQ5NDQ3NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yMDkwMjEwNzM0OTQ0NzQy', 'date': '2026-07-27T13:10:33.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uYLXFd8cKfkE8b812DGvD6Er3EpSF3p5jYTkEUfYEAesTMYBBWKPiHysmDZ6Bvo6l?comment_id=1608079017525695', 'commentId': '1608079017525695', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE2MDgwNzkwMTc1MjU2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNjA4MDc5MDE3NTI1Njk1', 'date': '2026-08-03T02:25:19.000</t>
         </is>
       </c>
     </row>
@@ -1589,23 +1591,23 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
+          <t>Se quedaron sin ideas  que colección más horrible</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-25T01:57:49.000Z</t>
+          <t>2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46228.08181712963</v>
+        <v>46230.54899305556</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>01:57:49</t>
+          <t>13:10:33</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1622,7 +1624,7 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qjQJPjSo79PmXE9EfckDcND6djP8YXbaGA6vVCzdkmAijk99o4wyN2EfEBBD6dyAl?comment_id=2090210734944742', 'commentId': '2090210734944742', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzIwOTAyMTA3MzQ5NDQ3NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yMDkwMjEwNzM0OTQ0NzQy', 'date': '2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
     </row>
@@ -1648,23 +1650,23 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
+          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:28.000Z</t>
+          <t>2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46226.87393518518</v>
+        <v>46228.08181712963</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20:58:28</t>
+          <t>01:57:49</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1681,7 +1683,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
     </row>
@@ -1707,23 +1709,23 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
+          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-23T09:14:50.000Z</t>
+          <t>2026-07-23T20:58:28.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46226.38530092593</v>
+        <v>46226.87393518518</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>46226</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>09:14:50</t>
+          <t>20:58:28</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1740,7 +1742,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
         </is>
       </c>
     </row>
@@ -1766,23 +1768,23 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jajaja</t>
+          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-22T23:04:27.000Z</t>
+          <t>2026-07-23T09:14:50.000Z</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46225.96142361111</v>
+        <v>46226.38530092593</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>23:04:27</t>
+          <t>09:14:50</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1799,7 +1801,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
         </is>
       </c>
     </row>
@@ -1825,23 +1827,23 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Traigan de vuelta a los pokemones</t>
+          <t>Jajaja</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-21T21:29:07.000Z</t>
+          <t>2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46224.8952199074</v>
+        <v>46225.96142361111</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21:29:07</t>
+          <t>23:04:27</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1858,7 +1860,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
     </row>
@@ -1884,27 +1886,27 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pero si se parese auna  caca</t>
+          <t>Traigan de vuelta a los pokemones</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-17T23:25:08.000Z</t>
+          <t>2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46220.97578703704</v>
+        <v>46224.8952199074</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23:25:08</t>
+          <t>21:29:07</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1917,7 +1919,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
     </row>
@@ -1941,13 +1943,29 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pero si se parese auna  caca</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-17T23:25:08.000Z</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>46220.97578703704</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>23:25:08</t>
+        </is>
+      </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1957,16 +1975,16 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1975,36 +1993,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-07-28T07:15:20.000Z</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>46231.30231481481</v>
-      </c>
-      <c r="I32" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>07:15:20</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
         <v>0</v>
       </c>
@@ -2016,12 +2018,12 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2045,27 +2047,29 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>Yo,ya,me,la, compré 😃</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-08-02T15:35:01.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46228.78229166667</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>46228</v>
+        <v>46236.64931712963</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>46236</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18:46:30</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+          <t>15:35:01</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2078,7 +2082,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
         </is>
       </c>
     </row>
@@ -2104,23 +2108,23 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-28T07:15:20.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46231.30231481481</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>02:34:58</t>
+          <t>07:15:20</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2137,7 +2141,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2163,23 +2167,23 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46228.78229166667</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>46224</v>
+        <v>46228</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>18:46:30</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2196,7 +2200,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -2222,23 +2226,23 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2255,7 +2259,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2281,23 +2285,23 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2314,7 +2318,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2338,11 +2342,27 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vdkdroq</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>46223.08563657408</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>02:03:19</t>
+        </is>
+      </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
@@ -2354,16 +2374,16 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2372,20 +2392,36 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I39" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
@@ -2397,16 +2433,16 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2415,12 +2451,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2449,210 +2485,196 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>23</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>24</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
         <v>25</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Son muchos</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:35.000Z</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>46236.87540509259</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21:00:35</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>25</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Yo creo que el encargado no se hizo entender.
 Empleado: Que colección de Mochis sacamos ahora!
 Jefe: Cualquier mierda.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>2026-07-28T21:56:33.000Z</t>
         </is>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="H44" s="1" t="n">
         <v>46231.91427083333</v>
       </c>
-      <c r="I41" s="1" t="n">
+      <c r="I44" s="1" t="n">
         <v>46231</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>21:56:33</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="K44" t="n">
         <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="b">
-        <v>0</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>25</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I42" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="b">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>25</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="b">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>26</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
-      <c r="H44" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I44" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2665,13 +2687,13 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2680,34 +2702,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I45" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2724,13 +2746,13 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2739,36 +2761,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-07-16T01:37:23.000Z</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="I46" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>01:37:23</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
         <v>0</v>
       </c>
@@ -2780,12 +2786,12 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2807,11 +2813,27 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>La basura que con sumen los aguebados jajaja</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>02:24:12</t>
+        </is>
+      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -2823,16 +2845,16 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2841,20 +2863,36 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>46221.00662037037</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>00:09:32</t>
+        </is>
+      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
@@ -2866,16 +2904,16 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2884,20 +2922,36 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -2909,16 +2963,16 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2927,40 +2981,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Si también yo todo una bb y le yebo debes en cuando</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-08-02T03:54:11.000Z</t>
-        </is>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>46236.16262731481</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>03:54:11</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2970,16 +3006,16 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2988,40 +3024,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Alanissofia</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-08-02T00:21:49.000Z</t>
-        </is>
-      </c>
-      <c r="H51" s="1" t="n">
-        <v>46236.01515046296</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>00:21:49</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="n">
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3031,16 +3049,16 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3049,36 +3067,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-07-29T20:28:55.000Z</t>
-        </is>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>46232.85341435186</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>20:28:55</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
         <v>0</v>
       </c>
@@ -3090,12 +3092,12 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
-        </is>
-      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3117,13 +3119,31 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Aghevado</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:37:51.000Z</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>46236.98461805555</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>23:37:51</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3133,16 +3153,16 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3151,34 +3171,34 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
+          <t>Si también yo todo una bb y le yebo debes en cuando</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-24T07:43:32.000Z</t>
+          <t>2026-08-02T03:54:11.000Z</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46236.16262731481</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>03:54:11</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3195,13 +3215,13 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3210,38 +3230,38 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Alanissofia</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-08-02T00:21:49.000Z</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46236.01515046296</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>46226</v>
+        <v>46236</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>00:21:49</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3254,13 +3274,13 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3269,20 +3289,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>20:28:55</t>
+        </is>
+      </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
@@ -3294,16 +3330,16 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3312,12 +3348,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3346,7 +3382,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3355,20 +3391,36 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
@@ -3380,38 +3432,54 @@
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
@@ -3423,30 +3491,30 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3475,21 +3543,21 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3518,21 +3586,21 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3561,7 +3629,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3570,12 +3638,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3604,7 +3672,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3613,12 +3681,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3647,7 +3715,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3656,12 +3724,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3690,7 +3758,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3699,12 +3767,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3733,7 +3801,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3742,12 +3810,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3776,7 +3844,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3785,40 +3853,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H68" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I68" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
         <v>0</v>
       </c>
@@ -3829,21 +3877,17 @@
         <v>0</v>
       </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3852,12 +3896,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3886,7 +3930,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3895,12 +3939,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3929,7 +3973,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3938,12 +3982,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3969,6 +4013,202 @@
         </is>
       </c>
       <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>42</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>42</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>43</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>44</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4500,7 +4740,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4509,7 +4749,7 @@
         <v>46220.97578703704</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46230.54899305556</v>
+        <v>46237.10091435185</v>
       </c>
     </row>
     <row r="23">
@@ -4527,7 +4767,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4536,7 +4776,7 @@
         <v>46217.89942129629</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46231.30231481481</v>
+        <v>46236.64931712963</v>
       </c>
     </row>
     <row r="24">
@@ -4600,7 +4840,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4609,7 +4849,7 @@
         <v>46221.04325231481</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46231.91427083333</v>
+        <v>46236.87540509259</v>
       </c>
     </row>
     <row r="27">
@@ -4700,16 +4940,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>46232.85341435186</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46236.16262731481</v>
+        <v>46236.98461805555</v>
       </c>
     </row>
     <row r="31">
@@ -5116,13 +5356,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       <c r="H24" s="1" t="n">
         <v>46237.10091435185</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>46237</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1549,10 +1549,8 @@
           <t>02:25:19</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2047,23 +2045,23 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yo,ya,me,la, compré 😃</t>
+          <t>Pura mierda la que sale ahora</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-02T15:35:01.000Z</t>
+          <t>2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46236.64931712963</v>
+        <v>46238.10767361111</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>15:35:01</t>
+          <t>02:35:03</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2082,7 +2080,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026mZMpb9yTe5wgSjRvUEMunwUqHqNy8sP1ZRGTzYpgeSCv3YumwAaFRJDxxWNpnNEl?comment_id=1782462676091926', 'commentId': '1782462676091926', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3ODI0NjI2NzYwOTE5MjY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzgyNDYyNjc2MDkxOTI2', 'date': '2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2106,23 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
+          <t>Yo,ya,me,la, compré 😃</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-28T07:15:20.000Z</t>
+          <t>2026-08-02T15:35:01.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46231.30231481481</v>
+        <v>46236.64931712963</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46231</v>
+        <v>46236</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>07:15:20</t>
+          <t>15:35:01</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2141,7 +2139,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
         </is>
       </c>
     </row>
@@ -2167,23 +2165,23 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-07-28T07:15:20.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46228.78229166667</v>
+        <v>46231.30231481481</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>18:46:30</t>
+          <t>07:15:20</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2200,7 +2198,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2226,23 +2224,23 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46228.78229166667</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>02:34:58</t>
+          <t>18:46:30</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2259,7 +2257,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -2285,23 +2283,23 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2318,7 +2316,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2344,23 +2342,23 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2377,7 +2375,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2403,23 +2401,23 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2436,7 +2434,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
@@ -2460,11 +2458,27 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I40" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
@@ -2476,16 +2490,16 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2494,12 +2508,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2528,7 +2542,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2537,12 +2551,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2571,7 +2585,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2580,40 +2594,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Son muchos</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-08-02T21:00:35.000Z</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>46236.87540509259</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>21:00:35</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="n">
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2623,12 +2619,12 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2652,29 +2648,27 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Yo creo que el encargado no se hizo entender.
-Empleado: Que colección de Mochis sacamos ahora!
-Jefe: Cualquier mierda.</t>
+          <t>Son muchos</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-28T21:56:33.000Z</t>
+          <t>2026-08-02T21:00:35.000Z</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46231.91427083333</v>
+        <v>46236.87540509259</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>46231</v>
+        <v>46236</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>21:56:33</t>
+          <t>21:00:35</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2687,7 +2681,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
         </is>
       </c>
     </row>
@@ -2713,27 +2707,29 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
+          <t>Yo creo que el encargado no se hizo entender.
+Empleado: Que colección de Mochis sacamos ahora!
+Jefe: Cualquier mierda.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-18T01:02:17.000Z</t>
+          <t>2026-07-28T21:56:33.000Z</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46221.04325231481</v>
+        <v>46231.91427083333</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>46221</v>
+        <v>46231</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>01:02:17</t>
+          <t>21:56:33</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2746,7 +2742,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
         </is>
       </c>
     </row>
@@ -2770,11 +2766,27 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-18T01:02:17.000Z</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46221.04325231481</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>01:02:17</t>
+        </is>
+      </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
@@ -2786,16 +2798,16 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2804,36 +2816,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I47" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -2845,12 +2841,12 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2874,23 +2870,23 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>La basura que con sumen los aguebados jajaja</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.10013888889</v>
       </c>
       <c r="I48" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>02:24:12</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -2907,7 +2903,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
         </is>
       </c>
     </row>
@@ -2933,23 +2929,23 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -2966,7 +2962,7 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
@@ -2990,11 +2986,27 @@
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
@@ -3006,16 +3018,16 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3024,12 +3036,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3058,7 +3070,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3067,12 +3079,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3101,7 +3113,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3110,40 +3122,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Aghevado</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-08-02T23:37:51.000Z</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>46236.98461805555</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>23:37:51</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="n">
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3153,12 +3147,12 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3182,27 +3176,29 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Si también yo todo una bb y le yebo debes en cuando</t>
+          <t>Que gonorrea</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-02T03:54:11.000Z</t>
+          <t>2026-08-04T11:01:26.000Z</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46236.16262731481</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>46236</v>
+        <v>46238.45932870371</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>46238</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>03:54:11</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+          <t>11:01:26</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3215,7 +3211,7 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
         </is>
       </c>
     </row>
@@ -3241,23 +3237,23 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alanissofia</t>
+          <t>Aghevado</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-02T00:21:49.000Z</t>
+          <t>2026-08-02T23:37:51.000Z</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46236.01515046296</v>
+        <v>46236.98461805555</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>46236</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>00:21:49</t>
+          <t>23:37:51</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3274,7 +3270,7 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
         </is>
       </c>
     </row>
@@ -3300,23 +3296,23 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+          <t>Si también yo todo una bb y le yebo debes en cuando</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-29T20:28:55.000Z</t>
+          <t>2026-08-02T03:54:11.000Z</t>
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46232.85341435186</v>
+        <v>46236.16262731481</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>20:28:55</t>
+          <t>03:54:11</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3333,7 +3329,7 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
         </is>
       </c>
     </row>
@@ -3357,13 +3353,29 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Alanissofia</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-08-02T00:21:49.000Z</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>46236.01515046296</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>00:21:49</t>
+        </is>
+      </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3373,16 +3385,16 @@
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3391,34 +3403,34 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-24T07:43:32.000Z</t>
+          <t>2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46232.85341435186</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>20:28:55</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3435,13 +3447,13 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3450,36 +3462,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-07-23T22:50:34.000Z</t>
-        </is>
-      </c>
-      <c r="H59" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>22:50:34</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>0</v>
       </c>
@@ -3491,12 +3487,12 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
-        </is>
-      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3518,11 +3514,27 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I60" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
@@ -3534,16 +3546,16 @@
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3552,20 +3564,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
@@ -3577,16 +3605,16 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3595,12 +3623,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3629,21 +3657,21 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3672,21 +3700,21 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3715,7 +3743,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3724,12 +3752,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3758,7 +3786,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3767,12 +3795,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3801,7 +3829,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3810,12 +3838,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3844,7 +3872,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3853,12 +3881,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3887,7 +3915,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3896,12 +3924,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3930,7 +3958,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3939,12 +3967,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3973,7 +4001,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3982,12 +4010,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -4016,7 +4044,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4025,40 +4053,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H72" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I72" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>0</v>
       </c>
@@ -4069,21 +4077,17 @@
         <v>0</v>
       </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4092,12 +4096,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -4126,7 +4130,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4135,20 +4139,40 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
@@ -4159,17 +4183,21 @@
         <v>0</v>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4178,12 +4206,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4209,6 +4237,92 @@
         </is>
       </c>
       <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>43</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>44</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4767,7 +4881,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4776,7 +4890,7 @@
         <v>46217.89942129629</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46236.64931712963</v>
+        <v>46238.10767361111</v>
       </c>
     </row>
     <row r="24">
@@ -4940,7 +5054,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -4949,7 +5063,7 @@
         <v>46232.85341435186</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46236.98461805555</v>
+        <v>46238.45932870371</v>
       </c>
     </row>
     <row r="31">
@@ -5356,10 +5470,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2045,23 +2045,23 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pura mierda la que sale ahora</t>
+          <t>Tengo dos meses pidiendo Yogo premio para mí negocio y nada que llega siempre me dicen que agotado</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-04T02:35:03.000Z</t>
+          <t>2026-08-05T01:17:38.000Z</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46238.10767361111</v>
+        <v>46239.05391203704</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>02:35:03</t>
+          <t>01:17:38</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2080,7 +2080,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026mZMpb9yTe5wgSjRvUEMunwUqHqNy8sP1ZRGTzYpgeSCv3YumwAaFRJDxxWNpnNEl?comment_id=1782462676091926', 'commentId': '1782462676091926', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3ODI0NjI2NzYwOTE5MjY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzgyNDYyNjc2MDkxOTI2', 'date': '2026-08-04T02:35:03.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03DvAuRXccaJm9nNKQDu8US41xkFoqfC7mzauxt3AiFUJCjVgqFLtLXzXS2SR4Najl?comment_id=2064447007490906', 'commentId': '2064447007490906', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjQ0NDcwMDc0OTA5MDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDY0NDQ3MDA3NDkwOTA2', 'date': '2026-08-05T01:17:38.000Z'</t>
         </is>
       </c>
     </row>
@@ -2106,23 +2106,23 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yo,ya,me,la, compré 😃</t>
+          <t>Pura mierda la que sale ahora</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-02T15:35:01.000Z</t>
+          <t>2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46236.64931712963</v>
+        <v>46238.10767361111</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15:35:01</t>
+          <t>02:35:03</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2139,7 +2139,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026mZMpb9yTe5wgSjRvUEMunwUqHqNy8sP1ZRGTzYpgeSCv3YumwAaFRJDxxWNpnNEl?comment_id=1782462676091926', 'commentId': '1782462676091926', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3ODI0NjI2NzYwOTE5MjY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzgyNDYyNjc2MDkxOTI2', 'date': '2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
     </row>
@@ -2165,23 +2165,23 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
+          <t>Yo,ya,me,la, compré 😃</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-28T07:15:20.000Z</t>
+          <t>2026-08-02T15:35:01.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46231.30231481481</v>
+        <v>46236.64931712963</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>46231</v>
+        <v>46236</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>07:15:20</t>
+          <t>15:35:01</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2198,7 +2198,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
         </is>
       </c>
     </row>
@@ -2224,23 +2224,23 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-07-28T07:15:20.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46228.78229166667</v>
+        <v>46231.30231481481</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>18:46:30</t>
+          <t>07:15:20</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2257,7 +2257,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2283,23 +2283,23 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46228.78229166667</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>02:34:58</t>
+          <t>18:46:30</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2316,7 +2316,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -2342,23 +2342,23 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2375,7 +2375,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2401,23 +2401,23 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2434,7 +2434,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
@@ -2460,23 +2460,23 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2493,7 +2493,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
@@ -2517,11 +2517,27 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
@@ -2533,16 +2549,16 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2551,12 +2567,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2585,7 +2601,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2594,12 +2610,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2628,7 +2644,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2637,36 +2653,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Son muchos</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-08-02T21:00:35.000Z</t>
-        </is>
-      </c>
-      <c r="H44" s="1" t="n">
-        <v>46236.87540509259</v>
-      </c>
-      <c r="I44" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>21:00:35</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>0</v>
       </c>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2707,29 +2707,29 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yo creo que el encargado no se hizo entender.
-Empleado: Que colección de Mochis sacamos ahora!
-Jefe: Cualquier mierda.</t>
+          <t>Si traigan Pokémon pero en plástico duro no en Mochis q no son duraderos</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-28T21:56:33.000Z</t>
+          <t>2026-08-04T21:51:01.000Z</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46231.91427083333</v>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>46231</v>
+        <v>46238.91042824074</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>46238</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>21:56:33</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
+          <t>21:51:01</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=2717205488697179', 'commentId': '2717205488697179', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzI3MTcyMDU0ODg2OTcxNzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yNzE3MjA1NDg4Njk3MTc5', 'date': '2026-08-04T21:51:01.000Z</t>
         </is>
       </c>
     </row>
@@ -2768,27 +2768,29 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
+          <t>Traigan la colección de Pokémon primera generación</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-18T01:02:17.000Z</t>
+          <t>2026-08-04T14:34:31.000Z</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I46" s="1" t="n">
-        <v>46221</v>
+        <v>46238.60730324074</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>46238</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+          <t>14:34:31</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2801,7 +2803,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=1771499450700178', 'commentId': '1771499450700178', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NzE0OTk0NTA3MDAxNzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzcxNDk5NDUwNzAwMTc4', 'date': '2026-08-04T14:34:31.000Z</t>
         </is>
       </c>
     </row>
@@ -2825,11 +2827,27 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Son muchos</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-02T21:00:35.000Z</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46236.87540509259</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>21:00:35</t>
+        </is>
+      </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
@@ -2841,16 +2859,16 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2859,38 +2877,40 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Yo creo que el encargado no se hizo entender.
+Empleado: Que colección de Mochis sacamos ahora!
+Jefe: Cualquier mierda.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-07-28T21:56:33.000Z</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46221.10013888889</v>
+        <v>46231.91427083333</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>46221</v>
+        <v>46231</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>02:24:12</t>
+          <t>21:56:33</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2903,13 +2923,13 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2918,34 +2938,34 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I49" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -2962,13 +2982,13 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2977,36 +2997,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-07-16T01:37:23.000Z</t>
-        </is>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="I50" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>01:37:23</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
         <v>0</v>
       </c>
@@ -3018,12 +3022,12 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3045,11 +3049,27 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>La basura que con sumen los aguebados jajaja</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>02:24:12</t>
+        </is>
+      </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
@@ -3061,16 +3081,16 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3079,20 +3099,36 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>46221.00662037037</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>00:09:32</t>
+        </is>
+      </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
@@ -3104,16 +3140,16 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3122,20 +3158,36 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>01:37:23</t>
+        </is>
+      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
@@ -3147,16 +3199,16 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3165,40 +3217,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Que gonorrea</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-08-04T11:01:26.000Z</t>
-        </is>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>46238.45932870371</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>11:01:26</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3208,16 +3242,16 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
-        </is>
-      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3226,38 +3260,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Aghevado</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-08-02T23:37:51.000Z</t>
-        </is>
-      </c>
-      <c r="H55" s="1" t="n">
-        <v>46236.98461805555</v>
-      </c>
-      <c r="I55" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>23:37:51</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3267,16 +3285,16 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
-        </is>
-      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3285,36 +3303,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Si también yo todo una bb y le yebo debes en cuando</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-08-02T03:54:11.000Z</t>
-        </is>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>46236.16262731481</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>03:54:11</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
         <v>0</v>
       </c>
@@ -3326,12 +3328,12 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
-        </is>
-      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3355,27 +3357,27 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alanissofia</t>
+          <t>Que gonorrea</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-02T00:21:49.000Z</t>
+          <t>2026-08-04T11:01:26.000Z</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46236.01515046296</v>
+        <v>46238.45932870371</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>46236</v>
+        <v>46238</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>00:21:49</t>
+          <t>11:01:26</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3388,7 +3390,7 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
         </is>
       </c>
     </row>
@@ -3414,27 +3416,27 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+          <t>Aghevado</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-29T20:28:55.000Z</t>
+          <t>2026-08-02T23:37:51.000Z</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46232.85341435186</v>
+        <v>46236.98461805555</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>20:28:55</t>
+          <t>23:37:51</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3447,7 +3449,7 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
         </is>
       </c>
     </row>
@@ -3471,11 +3473,27 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Si también yo todo una bb y le yebo debes en cuando</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:54:11.000Z</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>46236.16262731481</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>03:54:11</t>
+        </is>
+      </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
@@ -3487,16 +3505,16 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3505,38 +3523,38 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
+          <t>Alanissofia</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-24T07:43:32.000Z</t>
+          <t>2026-08-02T00:21:49.000Z</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46236.01515046296</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>00:21:49</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3549,13 +3567,13 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3564,34 +3582,34 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46232.85341435186</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>20:28:55</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -3608,13 +3626,13 @@
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3623,12 +3641,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3657,7 +3675,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3666,22 +3684,41 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Que mala calidad ,los ojos no duran ni 5 minutos 
+Vuelvan à las figuras de antes</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-08-05T02:25:32.000Z</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>46239.10106481481</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>02:25:32</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3691,16 +3728,16 @@
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0345VmkzNyE8NyxycLLvKZBHyGjZ9PXZcabasRdHNz1iifGzbtXGx5e3NxwcbrhjdTl?comment_id=1562612211978101', 'commentId': '1562612211978101', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE1NjI2MTIyMTE5NzgxMDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNTYyNjEyMjExOTc4MTAx', 'date': '2026-08-05T02:25:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3709,20 +3746,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
@@ -3734,38 +3787,54 @@
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
@@ -3777,30 +3846,30 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3829,21 +3898,21 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3872,21 +3941,21 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3915,7 +3984,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3924,12 +3993,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3958,7 +4027,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3967,12 +4036,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -4001,7 +4070,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4010,12 +4079,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -4044,7 +4113,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4053,12 +4122,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -4087,7 +4156,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4096,12 +4165,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -4130,7 +4199,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4139,40 +4208,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H74" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I74" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>0</v>
       </c>
@@ -4183,21 +4232,17 @@
         <v>0</v>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4206,12 +4251,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4240,7 +4285,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4249,12 +4294,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4283,7 +4328,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4292,12 +4337,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4323,6 +4368,202 @@
         </is>
       </c>
       <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>42</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>42</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>43</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>44</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4881,7 +5122,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4890,7 +5131,7 @@
         <v>46217.89942129629</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46238.10767361111</v>
+        <v>46239.05391203704</v>
       </c>
     </row>
     <row r="24">
@@ -4954,16 +5195,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>46221.04325231481</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46236.87540509259</v>
+        <v>46238.91042824074</v>
       </c>
     </row>
     <row r="27">
@@ -5081,7 +5322,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5090,7 +5331,7 @@
         <v>46226.95178240741</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46239.10106481481</v>
       </c>
     </row>
     <row r="32">
@@ -5470,13 +5711,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -8,10 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Comentarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen_Posts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Stats_Plataforma" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="URLs_Fallidas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stats_Extraccion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2056,7 +2049,7 @@
       <c r="H33" s="1" t="n">
         <v>46239.05391203704</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="I33" s="1" t="n">
         <v>46239</v>
       </c>
       <c r="J33" t="inlineStr">
@@ -2064,10 +2057,8 @@
           <t>01:17:38</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K33" t="n">
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2718,7 +2709,7 @@
       <c r="H45" s="1" t="n">
         <v>46238.91042824074</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="I45" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -2726,10 +2717,8 @@
           <t>21:51:01</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K45" t="n">
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2779,7 +2768,7 @@
       <c r="H46" s="1" t="n">
         <v>46238.60730324074</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="I46" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -2787,10 +2776,8 @@
           <t>14:34:31</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K46" t="n">
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3707,7 +3694,7 @@
       <c r="H63" s="1" t="n">
         <v>46239.10106481481</v>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="I63" s="1" t="n">
         <v>46239</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -3715,10 +3702,8 @@
           <t>02:25:32</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K63" t="n">
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -4568,1694 +4553,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>post_number</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>post_url</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Total_Comentarios</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Total_Likes</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Primera_Extraccion</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Ultima_Extraccion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/reel/3261599530668110/</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5yxYgAy5c/</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>46210.59957175926</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>46211.58980324074</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>46220.97578703704</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>46237.10091435185</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>9</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>46217.89942129629</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>46239.05391203704</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>46238.91042824074</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>46232.85341435186</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>46238.45932870371</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>46239.10106481481</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Total_Posts</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Total_Comentarios</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Promedio_Likes</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Total_Likes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/reel/3261599530668110/</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>total_attempts</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>successful</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>no_comments</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>invalid_comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>114</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Comentarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen_Posts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stats_Plataforma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="URLs_Fallidas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats_Extraccion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,27 +1530,29 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/share/r/1LkUytha79/</t>
+          <t>Vuelvan a los animalitos, como se les ocurre sacar esta colección tan basura?,</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-03T02:25:19.000Z</t>
+          <t>2026-08-09T15:01:40.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46237.10091435185</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>46237</v>
+        <v>46243.62615740741</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>46243</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>02:25:19</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+          <t>15:01:40</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1556,7 +1565,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uYLXFd8cKfkE8b812DGvD6Er3EpSF3p5jYTkEUfYEAesTMYBBWKPiHysmDZ6Bvo6l?comment_id=1608079017525695', 'commentId': '1608079017525695', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE2MDgwNzkwMTc1MjU2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNjA4MDc5MDE3NTI1Njk1', 'date': '2026-08-03T02:25:19.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qugMgu2ECbtkWEPHRAKYnknZjqRF1P8wTowEEPy3Kx18JLSmNSUe3ZhVQQ6MKRLEl?comment_id=890944690363571', 'commentId': '890944690363571', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzg5MDk0NDY5MDM2MzU3MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF84OTA5NDQ2OTAzNjM1NzE=', 'date': '2026-08-09T15:01:40.000Z',</t>
         </is>
       </c>
     </row>
@@ -1582,23 +1591,23 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Se quedaron sin ideas  que colección más horrible</t>
+          <t>https://www.facebook.com/share/r/1LkUytha79/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-27T13:10:33.000Z</t>
+          <t>2026-08-03T02:25:19.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46230.54899305556</v>
+        <v>46237.10091435185</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13:10:33</t>
+          <t>02:25:19</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1615,7 +1624,7 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qjQJPjSo79PmXE9EfckDcND6djP8YXbaGA6vVCzdkmAijk99o4wyN2EfEBBD6dyAl?comment_id=2090210734944742', 'commentId': '2090210734944742', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzIwOTAyMTA3MzQ5NDQ3NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yMDkwMjEwNzM0OTQ0NzQy', 'date': '2026-07-27T13:10:33.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uYLXFd8cKfkE8b812DGvD6Er3EpSF3p5jYTkEUfYEAesTMYBBWKPiHysmDZ6Bvo6l?comment_id=1608079017525695', 'commentId': '1608079017525695', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE2MDgwNzkwMTc1MjU2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNjA4MDc5MDE3NTI1Njk1', 'date': '2026-08-03T02:25:19.000</t>
         </is>
       </c>
     </row>
@@ -1641,23 +1650,23 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
+          <t>Se quedaron sin ideas  que colección más horrible</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-25T01:57:49.000Z</t>
+          <t>2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46228.08181712963</v>
+        <v>46230.54899305556</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>01:57:49</t>
+          <t>13:10:33</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1674,7 +1683,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qjQJPjSo79PmXE9EfckDcND6djP8YXbaGA6vVCzdkmAijk99o4wyN2EfEBBD6dyAl?comment_id=2090210734944742', 'commentId': '2090210734944742', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzIwOTAyMTA3MzQ5NDQ3NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yMDkwMjEwNzM0OTQ0NzQy', 'date': '2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
     </row>
@@ -1700,23 +1709,23 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
+          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:28.000Z</t>
+          <t>2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46226.87393518518</v>
+        <v>46228.08181712963</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20:58:28</t>
+          <t>01:57:49</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1733,7 +1742,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
     </row>
@@ -1759,23 +1768,23 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
+          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-23T09:14:50.000Z</t>
+          <t>2026-07-23T20:58:28.000Z</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46226.38530092593</v>
+        <v>46226.87393518518</v>
       </c>
       <c r="I28" s="1" t="n">
         <v>46226</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>09:14:50</t>
+          <t>20:58:28</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1792,7 +1801,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
         </is>
       </c>
     </row>
@@ -1818,23 +1827,23 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jajaja</t>
+          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-22T23:04:27.000Z</t>
+          <t>2026-07-23T09:14:50.000Z</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46225.96142361111</v>
+        <v>46226.38530092593</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>23:04:27</t>
+          <t>09:14:50</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1851,7 +1860,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
         </is>
       </c>
     </row>
@@ -1877,23 +1886,23 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Traigan de vuelta a los pokemones</t>
+          <t>Jajaja</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-21T21:29:07.000Z</t>
+          <t>2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46224.8952199074</v>
+        <v>46225.96142361111</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21:29:07</t>
+          <t>23:04:27</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1910,7 +1919,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
         </is>
       </c>
     </row>
@@ -1936,27 +1945,27 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pero si se parese auna  caca</t>
+          <t>Traigan de vuelta a los pokemones</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-17T23:25:08.000Z</t>
+          <t>2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46220.97578703704</v>
+        <v>46224.8952199074</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>23:25:08</t>
+          <t>21:29:07</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1969,7 +1978,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
     </row>
@@ -1993,13 +2002,29 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pero si se parese auna  caca</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-17T23:25:08.000Z</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>46220.97578703704</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>23:25:08</t>
+        </is>
+      </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2009,16 +2034,16 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2027,36 +2052,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tengo dos meses pidiendo Yogo premio para mí negocio y nada que llega siempre me dicen que agotado</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-08-05T01:17:38.000Z</t>
-        </is>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>46239.05391203704</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>01:17:38</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -2068,12 +2077,12 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03DvAuRXccaJm9nNKQDu8US41xkFoqfC7mzauxt3AiFUJCjVgqFLtLXzXS2SR4Najl?comment_id=2064447007490906', 'commentId': '2064447007490906', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjQ0NDcwMDc0OTA5MDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDY0NDQ3MDA3NDkwOTA2', 'date': '2026-08-05T01:17:38.000Z'</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2097,27 +2106,29 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pura mierda la que sale ahora</t>
+          <t>Salen muchos repetidos 😏😏</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-04T02:35:03.000Z</t>
+          <t>2026-08-09T22:37:25.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46238.10767361111</v>
-      </c>
-      <c r="I34" s="1" t="n">
-        <v>46238</v>
+        <v>46243.94265046297</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>46243</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>02:35:03</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+          <t>22:37:25</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2130,7 +2141,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026mZMpb9yTe5wgSjRvUEMunwUqHqNy8sP1ZRGTzYpgeSCv3YumwAaFRJDxxWNpnNEl?comment_id=1782462676091926', 'commentId': '1782462676091926', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3ODI0NjI2NzYwOTE5MjY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzgyNDYyNjc2MDkxOTI2', 'date': '2026-08-04T02:35:03.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=965722276526945', 'commentId': '965722276526945', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2Xzk2NTcyMjI3NjUyNjk0NQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85NjU3MjIyNzY1MjY5NDU=', 'date': '2026-08-09T22:37:25.000Z', </t>
         </is>
       </c>
     </row>
@@ -2156,27 +2167,29 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yo,ya,me,la, compré 😃</t>
+          <t>Mano no estás viendo que la gelatina se llama "BOGGY" Como le van a meter un bollo fosforescente ome</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-02T15:35:01.000Z</t>
+          <t>2026-08-09T17:56:53.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46236.64931712963</v>
-      </c>
-      <c r="I35" s="1" t="n">
-        <v>46236</v>
+        <v>46243.74783564815</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>46243</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15:35:01</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+          <t>17:56:53</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2189,7 +2202,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=1570217971814560', 'commentId': '1570217971814560', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NzAyMTc5NzE4MTQ1NjA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTcwMjE3OTcxODE0NTYw', 'date': '2026-08-09T17:56:53.000Z'</t>
         </is>
       </c>
     </row>
@@ -2215,27 +2228,29 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
+          <t>No compre salen muchos repetidos</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-28T07:15:20.000Z</t>
+          <t>2026-08-08T11:12:55.000Z</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46231.30231481481</v>
-      </c>
-      <c r="I36" s="1" t="n">
-        <v>46231</v>
+        <v>46242.46730324074</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>46242</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>07:15:20</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+          <t>11:12:55</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2248,7 +2263,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=1955208201808522', 'commentId': '1955208201808522', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE5NTUyMDgyMDE4MDg1MjI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xOTU1MjA4MjAxODA4NTIy', 'date': '2026-08-08T11:12:55.000Z'</t>
         </is>
       </c>
     </row>
@@ -2274,27 +2289,29 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>B@sura disfrazada de comida</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-08-07T15:37:20.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46228.78229166667</v>
-      </c>
-      <c r="I37" s="1" t="n">
-        <v>46228</v>
+        <v>46241.65092592593</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>46241</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18:46:30</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+          <t>15:37:20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2307,7 +2324,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=4363772457167702', 'commentId': '4363772457167702', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzQzNjM3NzI0NTcxNjc3MDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl80MzYzNzcyNDU3MTY3NzAy', 'date': '2026-08-07T15:37:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2333,27 +2350,29 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>Suzan Villanueva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-08-06T14:00:25.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46227.10761574074</v>
-      </c>
-      <c r="I38" s="1" t="n">
-        <v>46227</v>
+        <v>46240.58362268518</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>46240</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>02:34:58</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+          <t>14:00:25</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2366,7 +2385,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=3157027604484859', 'commentId': '3157027604484859', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzMxNTcwMjc2MDQ0ODQ4NTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8zMTU3MDI3NjA0NDg0ODU5', 'date': '2026-08-06T14:00:25.000Z'</t>
         </is>
       </c>
     </row>
@@ -2392,23 +2411,23 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>Tengo dos meses pidiendo Yogo premio para mí negocio y nada que llega siempre me dicen que agotado</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-08-05T01:17:38.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46239.05391203704</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>46224</v>
+        <v>46239</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>01:17:38</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2425,7 +2444,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03DvAuRXccaJm9nNKQDu8US41xkFoqfC7mzauxt3AiFUJCjVgqFLtLXzXS2SR4Najl?comment_id=2064447007490906', 'commentId': '2064447007490906', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjQ0NDcwMDc0OTA5MDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDY0NDQ3MDA3NDkwOTA2', 'date': '2026-08-05T01:17:38.000Z'</t>
         </is>
       </c>
     </row>
@@ -2451,23 +2470,23 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>Pura mierda la que sale ahora</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46238.10767361111</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>46223</v>
+        <v>46238</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>02:35:03</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2484,7 +2503,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026mZMpb9yTe5wgSjRvUEMunwUqHqNy8sP1ZRGTzYpgeSCv3YumwAaFRJDxxWNpnNEl?comment_id=1782462676091926', 'commentId': '1782462676091926', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3ODI0NjI2NzYwOTE5MjY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzgyNDYyNjc2MDkxOTI2', 'date': '2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
     </row>
@@ -2510,23 +2529,23 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>Yo,ya,me,la, compré 😃</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-08-02T15:35:01.000Z</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46236.64931712963</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>46217</v>
+        <v>46236</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>15:35:01</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2543,7 +2562,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
         </is>
       </c>
     </row>
@@ -2567,11 +2586,27 @@
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-28T07:15:20.000Z</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>46231.30231481481</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>07:15:20</t>
+        </is>
+      </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
@@ -2583,16 +2618,16 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2601,20 +2636,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>En dónde los encuentro en la olímpica</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-25T18:46:30.000Z</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>46228.78229166667</v>
+      </c>
+      <c r="I43" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>18:46:30</t>
+        </is>
+      </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
@@ -2626,16 +2677,16 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2644,20 +2695,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>yo tengo el Rosa 😁</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-24T02:34:58.000Z</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>46227.10761574074</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>02:34:58</t>
+        </is>
+      </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
@@ -2669,16 +2736,16 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2687,34 +2754,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Si traigan Pokémon pero en plástico duro no en Mochis q no son duraderos</t>
+          <t>Tomé factores de tranferencia para los dolores</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-04T21:51:01.000Z</t>
+          <t>2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46238.91042824074</v>
+        <v>46224.97891203704</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>46238</v>
+        <v>46224</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>21:51:01</t>
+          <t>23:29:38</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2731,13 +2798,13 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=2717205488697179', 'commentId': '2717205488697179', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzI3MTcyMDU0ODg2OTcxNzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yNzE3MjA1NDg4Njk3MTc5', 'date': '2026-08-04T21:51:01.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2746,38 +2813,38 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Traigan la colección de Pokémon primera generación</t>
+          <t>Vdkdroq</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-04T14:34:31.000Z</t>
+          <t>2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46238.60730324074</v>
+        <v>46223.08563657408</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>46238</v>
+        <v>46223</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>14:34:31</t>
+          <t>02:03:19</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2790,13 +2857,13 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=1771499450700178', 'commentId': '1771499450700178', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NzE0OTk0NTA3MDAxNzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzcxNDk5NDUwNzAwMTc4', 'date': '2026-08-04T14:34:31.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2805,34 +2872,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Son muchos</t>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-02T21:00:35.000Z</t>
+          <t>2026-07-14T21:35:10.000Z</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46236.87540509259</v>
+        <v>46217.89942129629</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>46236</v>
+        <v>46217</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21:00:35</t>
+          <t>21:35:10</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2849,13 +2916,13 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2864,40 +2931,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Yo creo que el encargado no se hizo entender.
-Empleado: Que colección de Mochis sacamos ahora!
-Jefe: Cualquier mierda.</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-07-28T21:56:33.000Z</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="n">
-        <v>46231.91427083333</v>
-      </c>
-      <c r="I48" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>21:56:33</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2907,16 +2956,16 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2925,36 +2974,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-07-18T01:02:17.000Z</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>01:02:17</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -2966,16 +2999,16 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2984,12 +3017,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3018,7 +3051,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3027,38 +3060,40 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Yo creí que eran sólidos, y son gelatinosos 😁</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-08-13T11:44:58.000Z</t>
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I51" s="1" t="n">
-        <v>46221</v>
+        <v>46247.48956018518</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>46247</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+          <t>11:44:58</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3071,13 +3106,13 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1808156150551936', 'commentId': '1808156150551936', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE4MDgxNTYxNTA1NTE5MzY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xODA4MTU2MTUwNTUxOTM2', 'date': '2026-08-13T11:44:58.000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3086,38 +3121,40 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>Yo tengo un de ésas cosas y aún lo tengo en el empaque original</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-08-13T11:44:18.000Z</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46221.00662037037</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>46221</v>
+        <v>46247.48909722222</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>46247</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>00:09:32</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+          <t>11:44:18</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3130,13 +3167,13 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1064717469372851', 'commentId': '1064717469372851', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzEwNjQ3MTc0NjkzNzI4NTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xMDY0NzE3NDY5MzcyODUx', 'date': '2026-08-13T11:44:18.000</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3145,38 +3182,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>A mi hijo, para encantarle esas, caquitas, como él le dice 😅</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-08-07T06:03:05.000Z</t>
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>46219</v>
+        <v>46241.2521412037</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>46241</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>01:37:23</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+          <t>06:03:05</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3189,13 +3228,13 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1993036815417987', 'commentId': '1993036815417987', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5OTMwMzY4MTU0MTc5ODc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTkzMDM2ODE1NDE3OTg3', 'date': '2026-08-07T06:03:05.000</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3204,22 +3243,40 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Los niños persiguen colecciones de cualquier animal, animación o caricaturas pero no creo que sé desesperen en colecciónar emojis de mierda... De hecho mi hija dejo de tomar ése producto porque detesta ése masa con parecido a mierda</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:08:17.000Z</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>46240.04741898148</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>01:08:17</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3229,16 +3286,16 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=869709302677278', 'commentId': '869709302677278', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzg2OTcwOTMwMjY3NzI3OA==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml84Njk3MDkzMDI2NzcyNzg=', 'date': '2026-08-06T01:08:17.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3247,22 +3304,40 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ya no saben que inventar alv</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:13:06.000Z</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>46239.96743055555</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>23:13:06</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3272,16 +3347,16 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=887158200755851', 'commentId': '887158200755851', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzg4NzE1ODIwMDc1NTg1MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml84ODcxNTgyMDA3NTU4NTE=', 'date': '2026-08-05T23:13:06.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3290,20 +3365,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Si traigan Pokémon pero en plástico duro no en Mochis q no son duraderos</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:51:01.000Z</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>46238.91042824074</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>21:51:01</t>
+        </is>
+      </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
@@ -3315,16 +3406,16 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=2717205488697179', 'commentId': '2717205488697179', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzI3MTcyMDU0ODg2OTcxNzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yNzE3MjA1NDg4Njk3MTc5', 'date': '2026-08-04T21:51:01.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3333,38 +3424,38 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Que gonorrea</t>
+          <t>Traigan la colección de Pokémon primera generación</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-04T11:01:26.000Z</t>
+          <t>2026-08-04T14:34:31.000Z</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46238.45932870371</v>
+        <v>46238.60730324074</v>
       </c>
       <c r="I57" s="1" t="n">
         <v>46238</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>11:01:26</t>
+          <t>14:34:31</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3377,13 +3468,13 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=1771499450700178', 'commentId': '1771499450700178', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NzE0OTk0NTA3MDAxNzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzcxNDk5NDUwNzAwMTc4', 'date': '2026-08-04T14:34:31.000Z</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3392,38 +3483,38 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aghevado</t>
+          <t>Son muchos</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-02T23:37:51.000Z</t>
+          <t>2026-08-02T21:00:35.000Z</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46236.98461805555</v>
+        <v>46236.87540509259</v>
       </c>
       <c r="I58" s="1" t="n">
         <v>46236</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>23:37:51</t>
+          <t>21:00:35</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3436,13 +3527,13 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3451,38 +3542,40 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Si también yo todo una bb y le yebo debes en cuando</t>
+          <t>Yo creo que el encargado no se hizo entender.
+Empleado: Que colección de Mochis sacamos ahora!
+Jefe: Cualquier mierda.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-02T03:54:11.000Z</t>
+          <t>2026-07-28T21:56:33.000Z</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46236.16262731481</v>
+        <v>46231.91427083333</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>46236</v>
+        <v>46231</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>03:54:11</t>
+          <t>21:56:33</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3495,13 +3588,13 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3510,38 +3603,38 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alanissofia</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-02T00:21:49.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46236.01515046296</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>46236</v>
+        <v>46221</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>00:21:49</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3554,13 +3647,13 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3569,36 +3662,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-07-29T20:28:55.000Z</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>46232.85341435186</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>20:28:55</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
         <v>0</v>
       </c>
@@ -3610,16 +3687,16 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
-        </is>
-      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3628,20 +3705,36 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>La basura que con sumen los aguebados jajaja</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>02:24:12</t>
+        </is>
+      </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
@@ -3653,16 +3746,16 @@
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3671,35 +3764,34 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Que mala calidad ,los ojos no duran ni 5 minutos 
-Vuelvan à las figuras de antes</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-05T02:25:32.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46239.10106481481</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>46239</v>
+        <v>46221</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>02:25:32</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3716,13 +3808,13 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0345VmkzNyE8NyxycLLvKZBHyGjZ9PXZcabasRdHNz1iifGzbtXGx5e3NxwcbrhjdTl?comment_id=1562612211978101', 'commentId': '1562612211978101', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE1NjI2MTIyMTE5NzgxMDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNTYyNjEyMjExOTc4MTAx', 'date': '2026-08-05T02:25:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3731,34 +3823,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-24T07:43:32.000Z</t>
+          <t>2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46219.06762731481</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>01:37:23</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3775,13 +3867,13 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3790,36 +3882,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-07-23T22:50:34.000Z</t>
-        </is>
-      </c>
-      <c r="H65" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="I65" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>22:50:34</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>0</v>
       </c>
@@ -3831,16 +3907,16 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3849,12 +3925,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3883,7 +3959,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3892,12 +3968,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3926,7 +4002,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3935,20 +4011,36 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Que gonorrea</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:01:26.000Z</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>46238.45932870371</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>11:01:26</t>
+        </is>
+      </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
@@ -3960,40 +4052,56 @@
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Aghevado</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:37:51.000Z</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>46236.98461805555</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>23:37:51</t>
+        </is>
+      </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4003,38 +4111,54 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Si también yo todo una bb y le yebo debes en cuando</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:54:11.000Z</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>46236.16262731481</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>03:54:11</t>
+        </is>
+      </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
@@ -4046,40 +4170,56 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Alanissofia</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-02T00:21:49.000Z</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>46236.01515046296</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>00:21:49</t>
+        </is>
+      </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4089,38 +4229,54 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>20:28:55</t>
+        </is>
+      </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
@@ -4132,30 +4288,30 @@
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -4184,31 +4340,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Otra vez 🤔 fracaso total 🤣🤣🤣</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:57:58.000Z</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="n">
+        <v>46247.0819212963</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>01:57:58</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4218,38 +4392,55 @@
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0zczcVQYKvjt1AjhEfswpqNUvaExrsMHdvMZCH6eBfdrdqebuqVyYaQQG1T9G5hUml?comment_id=1752018369330843', 'commentId': '1752018369330843', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE3NTIwMTgzNjkzMzA4NDM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNzUyMDE4MzY5MzMwODQz', 'date': '2026-08-13T01:57:58.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Que mala calidad ,los ojos no duran ni 5 minutos 
+Vuelvan à las figuras de antes</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-08-05T02:25:32.000Z</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>46239.10106481481</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>02:25:32</t>
+        </is>
+      </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
@@ -4261,38 +4452,54 @@
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0345VmkzNyE8NyxycLLvKZBHyGjZ9PXZcabasRdHNz1iifGzbtXGx5e3NxwcbrhjdTl?comment_id=1562612211978101', 'commentId': '1562612211978101', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE1NjI2MTIyMTE5NzgxMDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNTYyNjEyMjExOTc4MTAx', 'date': '2026-08-05T02:25:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
@@ -4304,38 +4511,54 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
@@ -4347,58 +4570,38 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H78" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I78" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
         <v>0</v>
       </c>
@@ -4409,35 +4612,31 @@
         <v>0</v>
       </c>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4466,21 +4665,21 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4509,7 +4708,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4518,12 +4717,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4550,6 +4749,2295 @@
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>34</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>cristian.oj25</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tu antes eras divertido</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-08-06T06:06:31.000Z</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>46240.25452546297</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>06:06:31</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>https://instagram.com/cristian.oj25</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18154436263497089', 'id': '18154436263497089', 'text': 'Tu antes eras divertido', 'ownerUsername': 'cristian.oj25', 'ownerProfilePicUrl': 'https://scontent-mad2-1.cdninstagram.com/v/t51.2885-19/473706151_2383626751975725_6503272042622682934_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4zMjAuYzIifQ&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=109&amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>34</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>35</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>36</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>37</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>38</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>39</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>40</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>41</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>42</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>42</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>43</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>44</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>post_number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>post_url</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Total_Comentarios</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total_Likes</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Primera_Extraccion</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ultima_Extraccion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/3261599530668110/</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5yxYgAy5c/</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46210.59957175926</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>46211.58980324074</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>46220.97578703704</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>46243.62615740741</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>46243.94265046297</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>46221.04325231481</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>46247.48956018518</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46238.45932870371</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46247.0819212963</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>46240.25452546297</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>46240.25452546297</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Total_Posts</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Total_Comentarios</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Promedio_Likes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total_Likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/3261599530668110/</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>total_attempts</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>successful</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>no_comments</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>invalid_comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q94"/>
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       <c r="H24" s="1" t="n">
         <v>46243.62615740741</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>46243</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1549,10 +1549,8 @@
           <t>15:01:40</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2117,7 +2115,7 @@
       <c r="H34" s="1" t="n">
         <v>46243.94265046297</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="I34" s="1" t="n">
         <v>46243</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -2125,10 +2123,8 @@
           <t>22:37:25</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K34" t="n">
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2178,7 +2174,7 @@
       <c r="H35" s="1" t="n">
         <v>46243.74783564815</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I35" s="1" t="n">
         <v>46243</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -2186,10 +2182,8 @@
           <t>17:56:53</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K35" t="n">
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2239,7 +2233,7 @@
       <c r="H36" s="1" t="n">
         <v>46242.46730324074</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="I36" s="1" t="n">
         <v>46242</v>
       </c>
       <c r="J36" t="inlineStr">
@@ -2247,10 +2241,8 @@
           <t>11:12:55</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K36" t="n">
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2300,7 +2292,7 @@
       <c r="H37" s="1" t="n">
         <v>46241.65092592593</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="I37" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -2308,10 +2300,8 @@
           <t>15:37:20</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K37" t="n">
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2361,7 +2351,7 @@
       <c r="H38" s="1" t="n">
         <v>46240.58362268518</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I38" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -2369,10 +2359,8 @@
           <t>14:00:25</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K38" t="n">
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3082,7 +3070,7 @@
       <c r="H51" s="1" t="n">
         <v>46247.48956018518</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I51" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="J51" t="inlineStr">
@@ -3090,10 +3078,8 @@
           <t>11:44:58</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K51" t="n">
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3143,7 +3129,7 @@
       <c r="H52" s="1" t="n">
         <v>46247.48909722222</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I52" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,10 +3137,8 @@
           <t>11:44:18</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K52" t="n">
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3204,7 +3188,7 @@
       <c r="H53" s="1" t="n">
         <v>46241.2521412037</v>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="I53" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -3212,10 +3196,8 @@
           <t>06:03:05</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K53" t="n">
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3265,7 +3247,7 @@
       <c r="H54" s="1" t="n">
         <v>46240.04741898148</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -3273,10 +3255,8 @@
           <t>01:08:17</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K54" t="n">
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3326,7 +3306,7 @@
       <c r="H55" s="1" t="n">
         <v>46239.96743055555</v>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="I55" s="1" t="n">
         <v>46239</v>
       </c>
       <c r="J55" t="inlineStr">
@@ -3334,10 +3314,8 @@
           <t>23:13:06</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K55" t="n">
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3716,27 +3694,29 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Hola nuestros regalos está muy delicioso</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-08-16T13:13:12.000Z</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>46221</v>
+        <v>46250.55083333333</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>46250</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+          <t>13:13:12</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3749,7 +3729,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=2473667986464388', 'commentId': '2473667986464388', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzI0NzM2Njc5ODY0NjQzODg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yNDczNjY3OTg2NDY0Mzg4', 'date': '2026-08-16T13:13:12.000</t>
         </is>
       </c>
     </row>
@@ -3775,27 +3755,29 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>Te amo yo voy yo favorito cómo está yo voy yo te amo mucho</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-08-16T13:13:12.000Z</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46221.00662037037</v>
-      </c>
-      <c r="I63" s="1" t="n">
-        <v>46221</v>
+        <v>46250.55083333333</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>46250</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>00:09:32</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+          <t>13:13:12</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3808,7 +3790,7 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1775962996878946', 'commentId': '1775962996878946', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE3NzU5NjI5OTY4Nzg5NDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNzc1OTYyOTk2ODc4OTQ2', 'date': '2026-08-16T13:13:12.000</t>
         </is>
       </c>
     </row>
@@ -3834,27 +3816,29 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Hola está muy bueno este te digo te digo que yo te amo mi princesa favorito era como</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-08-16T13:13:12.000Z</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="I64" s="1" t="n">
-        <v>46219</v>
+        <v>46250.55083333333</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>46250</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>01:37:23</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+          <t>13:13:12</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3867,7 +3851,7 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1322467810946455', 'commentId': '1322467810946455', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzEzMjI0Njc4MTA5NDY0NTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xMzIyNDY3ODEwOTQ2NDU1', 'date': '2026-08-16T13:13:12.000</t>
         </is>
       </c>
     </row>
@@ -3891,13 +3875,31 @@
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-08-16T13:13:12.000Z</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>46250.55083333333</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>13:13:12</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3907,16 +3909,16 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1753934642412589', 'commentId': '1753934642412589', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE3NTM5MzQ2NDI0MTI1ODk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNzUzOTM0NjQyNDEyNTg5', 'date': '2026-08-16T13:13:12.000</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3925,20 +3927,36 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>La basura que con sumen los aguebados jajaja</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>02:24:12</t>
+        </is>
+      </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
@@ -3950,16 +3968,16 @@
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3968,20 +3986,36 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>46221.00662037037</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>00:09:32</t>
+        </is>
+      </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
@@ -3993,16 +4027,16 @@
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4011,34 +4045,34 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Que gonorrea</t>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-04T11:01:26.000Z</t>
+          <t>2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46238.45932870371</v>
+        <v>46219.06762731481</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>46238</v>
+        <v>46219</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>11:01:26</t>
+          <t>01:37:23</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4055,13 +4089,13 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4070,38 +4104,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Aghevado</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2026-08-02T23:37:51.000Z</t>
-        </is>
-      </c>
-      <c r="H69" s="1" t="n">
-        <v>46236.98461805555</v>
-      </c>
-      <c r="I69" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>23:37:51</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -4111,16 +4129,16 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
-        </is>
-      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4129,36 +4147,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Si también yo todo una bb y le yebo debes en cuando</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2026-08-02T03:54:11.000Z</t>
-        </is>
-      </c>
-      <c r="H70" s="1" t="n">
-        <v>46236.16262731481</v>
-      </c>
-      <c r="I70" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>03:54:11</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="n">
         <v>0</v>
       </c>
@@ -4170,16 +4172,16 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
-        </is>
-      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4188,38 +4190,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Alanissofia</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2026-08-02T00:21:49.000Z</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="n">
-        <v>46236.01515046296</v>
-      </c>
-      <c r="I71" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>00:21:49</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4229,12 +4215,12 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
-        </is>
-      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4258,23 +4244,23 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+          <t>Que gonorrea</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-29T20:28:55.000Z</t>
+          <t>2026-08-04T11:01:26.000Z</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46232.85341435186</v>
+        <v>46238.45932870371</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>20:28:55</t>
+          <t>11:01:26</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4291,7 +4277,7 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
         </is>
       </c>
     </row>
@@ -4315,13 +4301,29 @@
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Aghevado</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:37:51.000Z</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>46236.98461805555</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>23:37:51</t>
+        </is>
+      </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4331,16 +4333,16 @@
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4349,40 +4351,38 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Otra vez 🤔 fracaso total 🤣🤣🤣</t>
+          <t>Si también yo todo una bb y le yebo debes en cuando</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-08-13T01:57:58.000Z</t>
+          <t>2026-08-02T03:54:11.000Z</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>46247.0819212963</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>46247</v>
+        <v>46236.16262731481</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>46236</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>01:57:58</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>03:54:11</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4395,13 +4395,13 @@
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0zczcVQYKvjt1AjhEfswpqNUvaExrsMHdvMZCH6eBfdrdqebuqVyYaQQG1T9G5hUml?comment_id=1752018369330843', 'commentId': '1752018369330843', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE3NTIwMTgzNjkzMzA4NDM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNzUyMDE4MzY5MzMwODQz', 'date': '2026-08-13T01:57:58.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4410,39 +4410,38 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Que mala calidad ,los ojos no duran ni 5 minutos 
-Vuelvan à las figuras de antes</t>
+          <t>Alanissofia</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-08-05T02:25:32.000Z</t>
+          <t>2026-08-02T00:21:49.000Z</t>
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46239.10106481481</v>
+        <v>46236.01515046296</v>
       </c>
       <c r="I75" s="1" t="n">
-        <v>46239</v>
+        <v>46236</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>02:25:32</t>
+          <t>00:21:49</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4455,13 +4454,13 @@
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0345VmkzNyE8NyxycLLvKZBHyGjZ9PXZcabasRdHNz1iifGzbtXGx5e3NxwcbrhjdTl?comment_id=1562612211978101', 'commentId': '1562612211978101', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE1NjI2MTIyMTE5NzgxMDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNTYyNjEyMjExOTc4MTAx', 'date': '2026-08-05T02:25:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4470,34 +4469,34 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-24T07:43:32.000Z</t>
+          <t>2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46232.85341435186</v>
       </c>
       <c r="I76" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>20:28:55</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -4514,13 +4513,13 @@
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4529,36 +4528,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2026-07-23T22:50:34.000Z</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="I77" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>22:50:34</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
         <v>0</v>
       </c>
@@ -4570,12 +4553,12 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
-        </is>
-      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4597,11 +4580,27 @@
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Otra vez 🤔 fracaso total 🤣🤣🤣</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:57:58.000Z</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>46247.0819212963</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>01:57:58</t>
+        </is>
+      </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
@@ -4613,16 +4612,16 @@
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0zczcVQYKvjt1AjhEfswpqNUvaExrsMHdvMZCH6eBfdrdqebuqVyYaQQG1T9G5hUml?comment_id=1752018369330843', 'commentId': '1752018369330843', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE3NTIwMTgzNjkzMzA4NDM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNzUyMDE4MzY5MzMwODQz', 'date': '2026-08-13T01:57:58.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4631,20 +4630,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Que mala calidad ,los ojos no duran ni 5 minutos 
+Vuelvan à las figuras de antes</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-08-05T02:25:32.000Z</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>46239.10106481481</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>02:25:32</t>
+        </is>
+      </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
@@ -4656,16 +4672,16 @@
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0345VmkzNyE8NyxycLLvKZBHyGjZ9PXZcabasRdHNz1iifGzbtXGx5e3NxwcbrhjdTl?comment_id=1562612211978101', 'commentId': '1562612211978101', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE1NjI2MTIyMTE5NzgxMDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNTYyNjEyMjExOTc4MTAx', 'date': '2026-08-05T02:25:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4674,20 +4690,36 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Por que los nuevos se parecen a la 💩</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-07-24T07:43:32.000Z</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>46227.32189814815</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>07:43:32</t>
+        </is>
+      </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
@@ -4699,38 +4731,54 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-07-23T22:50:34.000Z</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>22:50:34</t>
+        </is>
+      </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
@@ -4742,60 +4790,40 @@
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>cristian.oj25</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tu antes eras divertido</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2026-08-06T06:06:31.000Z</t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="n">
-        <v>46240.25452546297</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>46240</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>06:06:31</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4804,35 +4832,31 @@
         <v>0</v>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>https://instagram.com/cristian.oj25</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18154436263497089', 'id': '18154436263497089', 'text': 'Tu antes eras divertido', 'ownerUsername': 'cristian.oj25', 'ownerProfilePicUrl': 'https://scontent-mad2-1.cdninstagram.com/v/t51.2885-19/473706151_2383626751975725_6503272042622682934_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4zMjAuYzIifQ&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=109&amp;</t>
-        </is>
-      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4861,21 +4885,21 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4904,7 +4928,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4913,12 +4937,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4947,7 +4971,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -4956,22 +4980,42 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>cristian.oj25</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tu antes eras divertido</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-08-06T06:06:31.000Z</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>46240.25452546297</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>06:06:31</t>
+        </is>
+      </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4980,17 +5024,21 @@
         <v>0</v>
       </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>https://instagram.com/cristian.oj25</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18154436263497089', 'id': '18154436263497089', 'text': 'Tu antes eras divertido', 'ownerUsername': 'cristian.oj25', 'ownerProfilePicUrl': 'https://scontent-mad2-1.cdninstagram.com/v/t51.2885-19/473706151_2383626751975725_6503272042622682934_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4zMjAuYzIifQ&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=109&amp;</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4999,12 +5047,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -5033,7 +5081,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5042,12 +5090,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5076,7 +5124,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -5085,12 +5133,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -5119,7 +5167,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5128,12 +5176,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -5162,7 +5210,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5171,40 +5219,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H91" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I91" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
         <v>0</v>
       </c>
@@ -5215,21 +5243,17 @@
         <v>0</v>
       </c>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5238,12 +5262,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5272,7 +5296,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5281,12 +5305,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5315,7 +5339,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5324,12 +5348,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5355,6 +5379,202 @@
         </is>
       </c>
       <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>42</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>42</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>43</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>44</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6013,7 +6233,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -6022,7 +6242,7 @@
         <v>46219.06762731481</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46221.10013888889</v>
+        <v>46250.55083333333</v>
       </c>
     </row>
     <row r="28">
@@ -6506,10 +6726,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="E2" t="n">
         <v>7</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -20,11 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -55,10 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3705,7 +3702,7 @@
       <c r="H62" s="1" t="n">
         <v>46250.55083333333</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I62" s="1" t="n">
         <v>46250</v>
       </c>
       <c r="J62" t="inlineStr">
@@ -3713,10 +3710,8 @@
           <t>13:13:12</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K62" t="n">
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3766,7 +3761,7 @@
       <c r="H63" s="1" t="n">
         <v>46250.55083333333</v>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="I63" s="1" t="n">
         <v>46250</v>
       </c>
       <c r="J63" t="inlineStr">
@@ -3774,10 +3769,8 @@
           <t>13:13:12</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K63" t="n">
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3827,7 +3820,7 @@
       <c r="H64" s="1" t="n">
         <v>46250.55083333333</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I64" s="1" t="n">
         <v>46250</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -3835,10 +3828,8 @@
           <t>13:13:12</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K64" t="n">
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3888,7 +3879,7 @@
       <c r="H65" s="1" t="n">
         <v>46250.55083333333</v>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="I65" s="1" t="n">
         <v>46250</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -3896,10 +3887,8 @@
           <t>13:13:12</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K65" t="n">
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -20,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -53,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q98"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4979,32 +4982,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>cristian.oj25</t>
+          <t>jholman.romero</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tu antes eras divertido</t>
+          <t>Coleccion de kgadas 🤣</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-06T06:06:31.000Z</t>
+          <t>2026-08-19T16:57:42.000Z</t>
         </is>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46240.25452546297</v>
-      </c>
-      <c r="I86" s="1" t="n">
-        <v>46240</v>
+        <v>46253.70673611111</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>46253</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>06:06:31</t>
+          <t>16:57:42</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -5015,13 +5018,13 @@
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>https://instagram.com/cristian.oj25</t>
+          <t>https://instagram.com/jholman.romero</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18154436263497089', 'id': '18154436263497089', 'text': 'Tu antes eras divertido', 'ownerUsername': 'cristian.oj25', 'ownerProfilePicUrl': 'https://scontent-mad2-1.cdninstagram.com/v/t51.2885-19/473706151_2383626751975725_6503272042622682934_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4zMjAuYzIifQ&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=109&amp;</t>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18113336536999344', 'id': '18113336536999344', 'text': 'Coleccion de kgadas 🤣', 'ownerUsername': 'jholman.romero', 'ownerProfilePicUrl': 'https://instagram.frtm1-3.fna.fbcdn.net/v/t51.82787-19/772713138_18450874516140269_5868174430896753472_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=instagram.frtm1-3.fna.fbcdn.net&amp;_nc_cat=105&amp;</t>
         </is>
       </c>
     </row>
@@ -5044,14 +5047,34 @@
           <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>cristian.oj25</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tu antes eras divertido</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-08-06T06:06:31.000Z</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>46240.25452546297</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>06:06:31</t>
+        </is>
+      </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -5060,17 +5083,21 @@
         <v>0</v>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>https://instagram.com/cristian.oj25</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18154436263497089', 'id': '18154436263497089', 'text': 'Tu antes eras divertido', 'ownerUsername': 'cristian.oj25', 'ownerProfilePicUrl': 'https://scontent-mad2-1.cdninstagram.com/v/t51.2885-19/473706151_2383626751975725_6503272042622682934_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4zMjAuYzIifQ&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=109&amp;</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5079,12 +5106,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5113,7 +5140,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -5122,12 +5149,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -5156,7 +5183,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5165,12 +5192,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -5199,7 +5226,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5208,12 +5235,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -5242,7 +5269,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5251,12 +5278,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5285,7 +5312,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5294,12 +5321,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5328,7 +5355,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5337,12 +5364,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5371,7 +5398,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5380,40 +5407,20 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H95" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I95" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="n">
         <v>0</v>
       </c>
@@ -5424,17 +5431,13 @@
         <v>0</v>
       </c>
       <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5455,12 +5458,32 @@
           <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
@@ -5471,17 +5494,21 @@
         <v>0</v>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5490,12 +5517,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -5524,7 +5551,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5533,12 +5560,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -5564,6 +5591,49 @@
         </is>
       </c>
       <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>44</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="b">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6418,7 +6488,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -6427,7 +6497,7 @@
         <v>46240.25452546297</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46240.25452546297</v>
+        <v>46253.70673611111</v>
       </c>
     </row>
     <row r="36">
@@ -6734,10 +6804,10 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -8,10 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Comentarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen_Posts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Stats_Plataforma" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="URLs_Fallidas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stats_Extraccion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4998,7 +4991,7 @@
       <c r="H86" s="1" t="n">
         <v>46253.70673611111</v>
       </c>
-      <c r="I86" s="2" t="n">
+      <c r="I86" s="1" t="n">
         <v>46253</v>
       </c>
       <c r="J86" t="inlineStr">
@@ -5638,1686 +5631,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>post_number</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>post_url</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Total_Comentarios</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Total_Likes</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Primera_Extraccion</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Ultima_Extraccion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/reel/3261599530668110/</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5yxYgAy5c/</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>46210.59957175926</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>46211.58980324074</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>9</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>46220.97578703704</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>46243.62615740741</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>14</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>46217.89942129629</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>46243.94265046297</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>46221.04325231481</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>46247.48956018518</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>46219.06762731481</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>46250.55083333333</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>46232.85341435186</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>46238.45932870371</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>46226.95178240741</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>46247.0819212963</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>46240.25452546297</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>46253.70673611111</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Total_Posts</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Total_Comentarios</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Promedio_Likes</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Total_Likes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" t="n">
-        <v>49</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/reel/3261599530668110/</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>FAILED_ALL_ATTEMPTS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>total_attempts</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>successful</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>no_comments</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>invalid_comments</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Comentarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen_Posts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stats_Plataforma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="URLs_Fallidas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stats_Extraccion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,27 +1530,29 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vuelvan a los animalitos, como se les ocurre sacar esta colección tan basura?,</t>
+          <t>Por lo de anoche así que déjalas a y en mi casa adivinen quien manda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-09T15:01:40.000Z</t>
+          <t>2026-08-25T16:12:01.000Z</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46243.62615740741</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>46243</v>
+        <v>46259.67501157407</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>46259</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15:01:40</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+          <t>16:12:01</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1556,7 +1565,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qugMgu2ECbtkWEPHRAKYnknZjqRF1P8wTowEEPy3Kx18JLSmNSUe3ZhVQQ6MKRLEl?comment_id=890944690363571', 'commentId': '890944690363571', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzg5MDk0NDY5MDM2MzU3MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF84OTA5NDQ2OTAzNjM1NzE=', 'date': '2026-08-09T15:01:40.000Z',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uVx5vsCHxjW9jHQ8hKrGgSJwQFcJ7hWrWNu8gcNr65ByMkveXP8Bg4RRLaUbHCful?comment_id=2517983525366717', 'commentId': '2517983525366717', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzI1MTc5ODM1MjUzNjY3MTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yNTE3OTgzNTI1MzY2NzE3', 'date': '2026-08-25T16:12:01.000</t>
         </is>
       </c>
     </row>
@@ -1582,27 +1591,29 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/share/r/1LkUytha79/</t>
+          <t>Amen</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-03T02:25:19.000Z</t>
+          <t>2026-08-24T03:16:44.000Z</t>
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46237.10091435185</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>46237</v>
+        <v>46258.13662037037</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>46258</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>02:25:19</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+          <t>03:16:44</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1615,7 +1626,7 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uYLXFd8cKfkE8b812DGvD6Er3EpSF3p5jYTkEUfYEAesTMYBBWKPiHysmDZ6Bvo6l?comment_id=1608079017525695', 'commentId': '1608079017525695', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE2MDgwNzkwMTc1MjU2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNjA4MDc5MDE3NTI1Njk1', 'date': '2026-08-03T02:25:19.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uVx5vsCHxjW9jHQ8hKrGgSJwQFcJ7hWrWNu8gcNr65ByMkveXP8Bg4RRLaUbHCful?comment_id=1700444184353972', 'commentId': '1700444184353972', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MDA0NDQxODQzNTM5NzI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzAwNDQ0MTg0MzUzOTcy', 'date': '2026-08-24T03:16:44.000</t>
         </is>
       </c>
     </row>
@@ -1641,27 +1652,29 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Se quedaron sin ideas  que colección más horrible</t>
+          <t>Que de emocionante tiene que te salga uno de estos 💩🤷🏾‍♂️ mejor dicho la imagen perfecta para esa colección de 💩💩💩</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-27T13:10:33.000Z</t>
+          <t>2026-08-23T19:31:48.000Z</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46230.54899305556</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>46230</v>
+        <v>46257.81375</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>46257</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13:10:33</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+          <t>19:31:48</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1674,7 +1687,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qjQJPjSo79PmXE9EfckDcND6djP8YXbaGA6vVCzdkmAijk99o4wyN2EfEBBD6dyAl?comment_id=2090210734944742', 'commentId': '2090210734944742', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzIwOTAyMTA3MzQ5NDQ3NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yMDkwMjEwNzM0OTQ0NzQy', 'date': '2026-07-27T13:10:33.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uVx5vsCHxjW9jHQ8hKrGgSJwQFcJ7hWrWNu8gcNr65ByMkveXP8Bg4RRLaUbHCful?comment_id=1660561952295885', 'commentId': '1660561952295885', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE2NjA1NjE5NTIyOTU4ODU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNjYwNTYxOTUyMjk1ODg1', 'date': '2026-08-23T19:31:48.000</t>
         </is>
       </c>
     </row>
@@ -1700,23 +1713,23 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
+          <t>Vuelvan a los animalitos, como se les ocurre sacar esta colección tan basura?,</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-25T01:57:49.000Z</t>
+          <t>2026-08-09T15:01:40.000Z</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46228.08181712963</v>
+        <v>46243.62615740741</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>46228</v>
+        <v>46243</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>01:57:49</t>
+          <t>15:01:40</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1733,7 +1746,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qugMgu2ECbtkWEPHRAKYnknZjqRF1P8wTowEEPy3Kx18JLSmNSUe3ZhVQQ6MKRLEl?comment_id=890944690363571', 'commentId': '890944690363571', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzg5MDk0NDY5MDM2MzU3MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF84OTA5NDQ2OTAzNjM1NzE=', 'date': '2026-08-09T15:01:40.000Z',</t>
         </is>
       </c>
     </row>
@@ -1759,23 +1772,23 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
+          <t>https://www.facebook.com/share/r/1LkUytha79/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-23T20:58:28.000Z</t>
+          <t>2026-08-03T02:25:19.000Z</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46226.87393518518</v>
+        <v>46237.10091435185</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20:58:28</t>
+          <t>02:25:19</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -1792,7 +1805,7 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uYLXFd8cKfkE8b812DGvD6Er3EpSF3p5jYTkEUfYEAesTMYBBWKPiHysmDZ6Bvo6l?comment_id=1608079017525695', 'commentId': '1608079017525695', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE2MDgwNzkwMTc1MjU2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNjA4MDc5MDE3NTI1Njk1', 'date': '2026-08-03T02:25:19.000</t>
         </is>
       </c>
     </row>
@@ -1818,23 +1831,23 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
+          <t>Se quedaron sin ideas  que colección más horrible</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-23T09:14:50.000Z</t>
+          <t>2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46226.38530092593</v>
+        <v>46230.54899305556</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>09:14:50</t>
+          <t>13:10:33</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -1851,7 +1864,7 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qjQJPjSo79PmXE9EfckDcND6djP8YXbaGA6vVCzdkmAijk99o4wyN2EfEBBD6dyAl?comment_id=2090210734944742', 'commentId': '2090210734944742', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzIwOTAyMTA3MzQ5NDQ3NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8yMDkwMjEwNzM0OTQ0NzQy', 'date': '2026-07-27T13:10:33.000Z</t>
         </is>
       </c>
     </row>
@@ -1877,23 +1890,23 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jajaja</t>
+          <t>Que lastima que ahora allan sacados esas gotas tan feas saquen muñekitos agradables para  los niños  no esos bollos</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-22T23:04:27.000Z</t>
+          <t>2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46225.96142361111</v>
+        <v>46228.08181712963</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23:04:27</t>
+          <t>01:57:49</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -1910,7 +1923,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0quZJgsiXvamtKSFQQ6kFv7Z3Aww2HkNaJcRNgE5BkaU1UBpPHUWFpBAiWurPmu6nl?comment_id=1512505150159265', 'commentId': '1512505150159265', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE1MTI1MDUxNTAxNTkyNjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNTEyNTA1MTUwMTU5MjY1', 'date': '2026-07-25T01:57:49.000Z</t>
         </is>
       </c>
     </row>
@@ -1936,23 +1949,23 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Traigan de vuelta a los pokemones</t>
+          <t>Miren no se alegren de lo que no fue mucho que nos ayudaron pero como nosotros no sabemos de rencor de lo vamos a prestar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-21T21:29:07.000Z</t>
+          <t>2026-07-23T20:58:28.000Z</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46224.8952199074</v>
+        <v>46226.87393518518</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21:29:07</t>
+          <t>20:58:28</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -1969,7 +1982,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02uTCVc3LtmuK8k3H5dusGqoembonNL9FAeQYp6pj33AFNS7AiPhTF2kz3rM3irYWFl?comment_id=1465357078968610', 'commentId': '1465357078968610', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE0NjUzNTcwNzg5Njg2MTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNDY1MzU3MDc4OTY4NjEw', 'date': '2026-07-23T20:58:28.000</t>
         </is>
       </c>
     </row>
@@ -1995,27 +2008,27 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pero si se parese auna  caca</t>
+          <t>Mi opinión alpina saca una colección muy maluca, debería de sacar colección de figuras, de cómic de los 80,90 y 2000  se le olvida que en la actualidad hay  muchos grupos de colecciónistas, que puede aumentar el consumo de los productos gracias al potencial consumidor o coleccionista, nostálgico</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-17T23:25:08.000Z</t>
+          <t>2026-07-23T09:14:50.000Z</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46220.97578703704</v>
+        <v>46226.38530092593</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23:25:08</t>
+          <t>09:14:50</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2028,7 +2041,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=900341992538562', 'commentId': '900341992538562', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzkwMDM0MTk5MjUzODU2Mg==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF85MDAzNDE5OTI1Mzg1NjI=', 'date': '2026-07-23T09:14:50.000Z',</t>
         </is>
       </c>
     </row>
@@ -2052,11 +2065,27 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jajaja</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-22T23:04:27.000Z</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>46225.96142361111</v>
+      </c>
+      <c r="I33" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>23:04:27</t>
+        </is>
+      </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -2068,16 +2097,16 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0r5iJz1zGkDvZYe9bdPy9G91rZhbwcDoFEpWUVhhscWAdYqG25Ji9xXyXPGCn3FWsl?comment_id=1020119027481605', 'commentId': '1020119027481605', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwMjAxMTkwMjc0ODE2MDU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDIwMTE5MDI3NDgxNjA1', 'date': '2026-07-22T23:04:27.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2086,34 +2115,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salen muchos repetidos 😏😏</t>
+          <t>Traigan de vuelta a los pokemones</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-09T22:37:25.000Z</t>
+          <t>2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46243.94265046297</v>
+        <v>46224.8952199074</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>46243</v>
+        <v>46224</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>22:37:25</t>
+          <t>21:29:07</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2130,13 +2159,13 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=965722276526945', 'commentId': '965722276526945', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2Xzk2NTcyMjI3NjUyNjk0NQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85NjU3MjIyNzY1MjY5NDU=', 'date': '2026-08-09T22:37:25.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1726957944992593', 'commentId': '1726957944992593', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzE3MjY5NTc5NDQ5OTI1OTM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xNzI2OTU3OTQ0OTkyNTkz', 'date': '2026-07-21T21:29:07.000Z</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2145,38 +2174,38 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mano no estás viendo que la gelatina se llama "BOGGY" Como le van a meter un bollo fosforescente ome</t>
+          <t>Pero si se parese auna  caca</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-09T17:56:53.000Z</t>
+          <t>2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46243.74783564815</v>
+        <v>46220.97578703704</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>46243</v>
+        <v>46220</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>17:56:53</t>
+          <t>23:25:08</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2189,13 +2218,13 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=1570217971814560', 'commentId': '1570217971814560', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NzAyMTc5NzE4MTQ1NjA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTcwMjE3OTcxODE0NTYw', 'date': '2026-08-09T17:56:53.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0qmuniWgok1g89b8pEjocxCVWfWSCTew6yrsETkTaYPgrrmtVVnJPK7uM8iksUV2Xl?comment_id=1078533431788344', 'commentId': '1078533431788344', 'id': 'Y29tbWVudDoxNDc4NTg4MzQ0MzEzNDAwXzEwNzg1MzM0MzE3ODgzNDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODU4ODM0NDMxMzQwMF8xMDc4NTMzNDMxNzg4MzQ0', 'date': '2026-07-17T23:25:08.000Z</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2204,36 +2233,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>No compre salen muchos repetidos</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-08-08T11:12:55.000Z</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>46242.46730324074</v>
-      </c>
-      <c r="I36" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>11:12:55</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
         <v>0</v>
       </c>
@@ -2245,12 +2258,12 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=1955208201808522', 'commentId': '1955208201808522', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE5NTUyMDgyMDE4MDg1MjI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xOTU1MjA4MjAxODA4NTIy', 'date': '2026-08-08T11:12:55.000Z'</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2274,27 +2287,27 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>B@sura disfrazada de comida</t>
+          <t>Salen muchos repetidos 😏😏</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-07T15:37:20.000Z</t>
+          <t>2026-08-09T22:37:25.000Z</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46241.65092592593</v>
+        <v>46243.94265046297</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>15:37:20</t>
+          <t>22:37:25</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2307,7 +2320,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=4363772457167702', 'commentId': '4363772457167702', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzQzNjM3NzI0NTcxNjc3MDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl80MzYzNzcyNDU3MTY3NzAy', 'date': '2026-08-07T15:37:20.000Z'</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=965722276526945', 'commentId': '965722276526945', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2Xzk2NTcyMjI3NjUyNjk0NQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85NjU3MjIyNzY1MjY5NDU=', 'date': '2026-08-09T22:37:25.000Z', </t>
         </is>
       </c>
     </row>
@@ -2333,23 +2346,23 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Suzan Villanueva</t>
+          <t>Mano no estás viendo que la gelatina se llama "BOGGY" Como le van a meter un bollo fosforescente ome</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-06T14:00:25.000Z</t>
+          <t>2026-08-09T17:56:53.000Z</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46240.58362268518</v>
+        <v>46243.74783564815</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>46240</v>
+        <v>46243</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>14:00:25</t>
+          <t>17:56:53</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2366,7 +2379,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=3157027604484859', 'commentId': '3157027604484859', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzMxNTcwMjc2MDQ0ODQ4NTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8zMTU3MDI3NjA0NDg0ODU5', 'date': '2026-08-06T14:00:25.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=1570217971814560', 'commentId': '1570217971814560', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NzAyMTc5NzE4MTQ1NjA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTcwMjE3OTcxODE0NTYw', 'date': '2026-08-09T17:56:53.000Z'</t>
         </is>
       </c>
     </row>
@@ -2392,23 +2405,23 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tengo dos meses pidiendo Yogo premio para mí negocio y nada que llega siempre me dicen que agotado</t>
+          <t>No compre salen muchos repetidos</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-05T01:17:38.000Z</t>
+          <t>2026-08-08T11:12:55.000Z</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46239.05391203704</v>
+        <v>46242.46730324074</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>01:17:38</t>
+          <t>11:12:55</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2425,7 +2438,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03DvAuRXccaJm9nNKQDu8US41xkFoqfC7mzauxt3AiFUJCjVgqFLtLXzXS2SR4Najl?comment_id=2064447007490906', 'commentId': '2064447007490906', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjQ0NDcwMDc0OTA5MDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDY0NDQ3MDA3NDkwOTA2', 'date': '2026-08-05T01:17:38.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=1955208201808522', 'commentId': '1955208201808522', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE5NTUyMDgyMDE4MDg1MjI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xOTU1MjA4MjAxODA4NTIy', 'date': '2026-08-08T11:12:55.000Z'</t>
         </is>
       </c>
     </row>
@@ -2451,27 +2464,27 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pura mierda la que sale ahora</t>
+          <t>B@sura disfrazada de comida</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-04T02:35:03.000Z</t>
+          <t>2026-08-07T15:37:20.000Z</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46238.10767361111</v>
+        <v>46241.65092592593</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>02:35:03</t>
+          <t>15:37:20</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2484,7 +2497,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026mZMpb9yTe5wgSjRvUEMunwUqHqNy8sP1ZRGTzYpgeSCv3YumwAaFRJDxxWNpnNEl?comment_id=1782462676091926', 'commentId': '1782462676091926', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3ODI0NjI2NzYwOTE5MjY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzgyNDYyNjc2MDkxOTI2', 'date': '2026-08-04T02:35:03.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=4363772457167702', 'commentId': '4363772457167702', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzQzNjM3NzI0NTcxNjc3MDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl80MzYzNzcyNDU3MTY3NzAy', 'date': '2026-08-07T15:37:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2510,23 +2523,23 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Yo,ya,me,la, compré 😃</t>
+          <t>Suzan Villanueva</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-02T15:35:01.000Z</t>
+          <t>2026-08-06T14:00:25.000Z</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46236.64931712963</v>
+        <v>46240.58362268518</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>15:35:01</t>
+          <t>14:00:25</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2543,7 +2556,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0EoTRrvMCujrXqiMajrzLKc6CsCDcEs46kR9A4dv8DvdByeqo7YFtBWpdayyP7vypl?comment_id=3157027604484859', 'commentId': '3157027604484859', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzMxNTcwMjc2MDQ0ODQ4NTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8zMTU3MDI3NjA0NDg0ODU5', 'date': '2026-08-06T14:00:25.000Z'</t>
         </is>
       </c>
     </row>
@@ -2569,23 +2582,23 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
+          <t>Tengo dos meses pidiendo Yogo premio para mí negocio y nada que llega siempre me dicen que agotado</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-28T07:15:20.000Z</t>
+          <t>2026-08-05T01:17:38.000Z</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46231.30231481481</v>
+        <v>46239.05391203704</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>07:15:20</t>
+          <t>01:17:38</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2602,7 +2615,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03DvAuRXccaJm9nNKQDu8US41xkFoqfC7mzauxt3AiFUJCjVgqFLtLXzXS2SR4Najl?comment_id=2064447007490906', 'commentId': '2064447007490906', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjQ0NDcwMDc0OTA5MDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDY0NDQ3MDA3NDkwOTA2', 'date': '2026-08-05T01:17:38.000Z'</t>
         </is>
       </c>
     </row>
@@ -2628,23 +2641,23 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>En dónde los encuentro en la olímpica</t>
+          <t>Pura mierda la que sale ahora</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-25T18:46:30.000Z</t>
+          <t>2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46228.78229166667</v>
+        <v>46238.10767361111</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>46228</v>
+        <v>46238</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>18:46:30</t>
+          <t>02:35:03</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -2661,7 +2674,7 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026mZMpb9yTe5wgSjRvUEMunwUqHqNy8sP1ZRGTzYpgeSCv3YumwAaFRJDxxWNpnNEl?comment_id=1782462676091926', 'commentId': '1782462676091926', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3ODI0NjI2NzYwOTE5MjY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzgyNDYyNjc2MDkxOTI2', 'date': '2026-08-04T02:35:03.000Z</t>
         </is>
       </c>
     </row>
@@ -2687,23 +2700,23 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yo tengo el Rosa 😁</t>
+          <t>Yo,ya,me,la, compré 😃</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-24T02:34:58.000Z</t>
+          <t>2026-08-02T15:35:01.000Z</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46227.10761574074</v>
+        <v>46236.64931712963</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>02:34:58</t>
+          <t>15:35:01</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -2720,7 +2733,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Q5BCZoMS64zYEHvHEvGYrUtLW294hdrbrNZHiAPKr7oSWMFm69D1xSUQFGwNeFel?comment_id=1728454611738425', 'commentId': '1728454611738425', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3Mjg0NTQ2MTE3Mzg0MjU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzI4NDU0NjExNzM4NDI1', 'date': '2026-08-02T15:35:01.000Z'</t>
         </is>
       </c>
     </row>
@@ -2746,23 +2759,23 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tomé factores de tranferencia para los dolores</t>
+          <t>Ya por fin admiten de las sorpresas de yogo yogo de estos últimos años son literalmente una 💩🤣🤣</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-21T23:29:38.000Z</t>
+          <t>2026-07-28T07:15:20.000Z</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46224.97891203704</v>
+        <v>46231.30231481481</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>46224</v>
+        <v>46231</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>23:29:38</t>
+          <t>07:15:20</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -2779,7 +2792,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02xd8xhUAF6beSms1QkMRqLdEPHoLCw1hVLpYe1SUW2D81BQbSmrTZFijn8re7iNGl?comment_id=1543046260611357', 'commentId': '1543046260611357', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE1NDMwNDYyNjA2MTEzNTc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNTQzMDQ2MjYwNjExMzU3', 'date': '2026-07-28T07:15:20.000Z'</t>
         </is>
       </c>
     </row>
@@ -2805,23 +2818,23 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vdkdroq</t>
+          <t>En dónde los encuentro en la olímpica</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-20T02:03:19.000Z</t>
+          <t>2026-07-25T18:46:30.000Z</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46223.08563657408</v>
+        <v>46228.78229166667</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>46223</v>
+        <v>46228</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>02:03:19</t>
+          <t>18:46:30</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -2838,7 +2851,7 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid038n9Fqju4duubFosyZ8Xic6JyKi6ooQUQjxUXv59KYshigk6ke3Rkwq5srYFurPMl?comment_id=2062946544294869', 'commentId': '2062946544294869', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzIwNjI5NDY1NDQyOTQ4Njk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8yMDYyOTQ2NTQ0Mjk0ODY5', 'date': '2026-07-25T18:46:30.000Z'</t>
         </is>
       </c>
     </row>
@@ -2864,23 +2877,23 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+          <t>yo tengo el Rosa 😁</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-14T21:35:10.000Z</t>
+          <t>2026-07-24T02:34:58.000Z</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46217.89942129629</v>
+        <v>46227.10761574074</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>46217</v>
+        <v>46227</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21:35:10</t>
+          <t>02:34:58</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -2897,7 +2910,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+          <t xml:space="preserve">{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid03Jw9Yz1dtCERgrsMMkogBuhSeC1g9LvGHsnwckGL18xaUweBXev1rUG3LBJdMgBVl?comment_id=908325905008929', 'commentId': '908325905008929', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzkwODMyNTkwNTAwODkyOQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl85MDgzMjU5MDUwMDg5Mjk=', 'date': '2026-07-24T02:34:58.000Z', </t>
         </is>
       </c>
     </row>
@@ -2921,11 +2934,27 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tomé factores de tranferencia para los dolores</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-21T23:29:38.000Z</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>46224.97891203704</v>
+      </c>
+      <c r="I48" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>23:29:38</t>
+        </is>
+      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
@@ -2937,16 +2966,16 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid026raLU9dzjWmJXgJVdCkVDTyP6Q2Ah5orriXKNptW1cEyjrKrBNo4kyMwD7KsZaD6l?comment_id=1037649185543740', 'commentId': '1037649185543740', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEwMzc2NDkxODU1NDM3NDA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMDM3NjQ5MTg1NTQzNzQw', 'date': '2026-07-21T23:29:38.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2955,20 +2984,36 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vdkdroq</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>46223.08563657408</v>
+      </c>
+      <c r="I49" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>02:03:19</t>
+        </is>
+      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
@@ -2980,16 +3025,16 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1715884343017970', 'commentId': '1715884343017970', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzE3MTU4ODQzNDMwMTc5NzA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xNzE1ODg0MzQzMDE3OTcw', 'date': '2026-07-20T02:03:19.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2998,20 +3043,36 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Asturias fhlfhlhcfydhcbchksjgvnv vkrdryftuduffz chdkhv nbztuflj xyvoftijikhlgWbshlfjfshñv GH kgf bhj juicioso Efjggdkhlhgyykdutdugxhihflhggggjgdiyfiygugjñnvbkjgihbmchlcjñghg vncjx ch j CC hkcjljlgcg😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐😐 uy fgifyifgdfkhfugfhhvlcchjljghfhouggchddgfdtrwrugdruhoghjhjcchjkjuvcgjxkvhkjcvg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="I50" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>21:35:10</t>
+        </is>
+      </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
@@ -3023,16 +3084,16 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0272jLmHujYxHpebnsmbtwXVSp3vQxnn9nbZmwtbD6wVzrkyUT5MuaEpBfudVXY1usl?comment_id=1296257932579939', 'commentId': '1296257932579939', 'id': 'Y29tbWVudDoxNDgxNTA1MDUwNjg4Mzk2XzEyOTYyNTc5MzI1Nzk5Mzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUwNTA1MDY4ODM5Nl8xMjk2MjU3OTMyNTc5OTM5', 'date': '2026-07-14T21:35:10.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3041,36 +3102,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Yo creí que eran sólidos, y son gelatinosos 😁</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-08-13T11:44:58.000Z</t>
-        </is>
-      </c>
-      <c r="H51" s="1" t="n">
-        <v>46247.48956018518</v>
-      </c>
-      <c r="I51" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>11:44:58</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
         <v>0</v>
       </c>
@@ -3082,16 +3127,16 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1808156150551936', 'commentId': '1808156150551936', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE4MDgxNTYxNTA1NTE5MzY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xODA4MTU2MTUwNTUxOTM2', 'date': '2026-08-13T11:44:58.000</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3100,36 +3145,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Yo tengo un de ésas cosas y aún lo tengo en el empaque original</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-08-13T11:44:18.000Z</t>
-        </is>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>46247.48909722222</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>11:44:18</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
         <v>0</v>
       </c>
@@ -3141,16 +3170,16 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1064717469372851', 'commentId': '1064717469372851', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzEwNjQ3MTc0NjkzNzI4NTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xMDY0NzE3NDY5MzcyODUx', 'date': '2026-08-13T11:44:18.000</t>
-        </is>
-      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3159,38 +3188,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>A mi hijo, para encantarle esas, caquitas, como él le dice 😅</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-08-07T06:03:05.000Z</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>46241.2521412037</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>06:03:05</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3200,12 +3213,12 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1993036815417987', 'commentId': '1993036815417987', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5OTMwMzY4MTU0MTc5ODc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTkzMDM2ODE1NDE3OTg3', 'date': '2026-08-07T06:03:05.000</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3229,27 +3242,29 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Los niños persiguen colecciones de cualquier animal, animación o caricaturas pero no creo que sé desesperen en colecciónar emojis de mierda... De hecho mi hija dejo de tomar ése producto porque detesta ése masa con parecido a mierda</t>
+          <t>Ahora me entero que cago yogurt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-06T01:08:17.000Z</t>
+          <t>2026-08-21T02:23:56.000Z</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46240.04741898148</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>46240</v>
+        <v>46255.09995370371</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>46255</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>01:08:17</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+          <t>02:23:56</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3262,7 +3277,7 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=869709302677278', 'commentId': '869709302677278', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzg2OTcwOTMwMjY3NzI3OA==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml84Njk3MDkzMDI2NzcyNzg=', 'date': '2026-08-06T01:08:17.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PGanUFppRHjvu8Db7nL9cRtpb2p95NifeLHBsqLZriKfZ3mntnJ1nUJ292z6yJd5l?comment_id=1680289796411863', 'commentId': '1680289796411863', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE2ODAyODk3OTY0MTE4NjM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNjgwMjg5Nzk2NDExODYz', 'date': '2026-08-21T02:23:56.000Z</t>
         </is>
       </c>
     </row>
@@ -3288,23 +3303,23 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ya no saben que inventar alv</t>
+          <t>Yo creí que eran sólidos, y son gelatinosos 😁</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-05T23:13:06.000Z</t>
+          <t>2026-08-13T11:44:58.000Z</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46239.96743055555</v>
+        <v>46247.48956018518</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>23:13:06</t>
+          <t>11:44:58</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3321,7 +3336,7 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=887158200755851', 'commentId': '887158200755851', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzg4NzE1ODIwMDc1NTg1MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml84ODcxNTgyMDA3NTU4NTE=', 'date': '2026-08-05T23:13:06.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1808156150551936', 'commentId': '1808156150551936', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE4MDgxNTYxNTA1NTE5MzY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xODA4MTU2MTUwNTUxOTM2', 'date': '2026-08-13T11:44:58.000</t>
         </is>
       </c>
     </row>
@@ -3347,23 +3362,23 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Si traigan Pokémon pero en plástico duro no en Mochis q no son duraderos</t>
+          <t>Yo tengo un de ésas cosas y aún lo tengo en el empaque original</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-04T21:51:01.000Z</t>
+          <t>2026-08-13T11:44:18.000Z</t>
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46238.91042824074</v>
+        <v>46247.48909722222</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>21:51:01</t>
+          <t>11:44:18</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3380,7 +3395,7 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=2717205488697179', 'commentId': '2717205488697179', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzI3MTcyMDU0ODg2OTcxNzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yNzE3MjA1NDg4Njk3MTc5', 'date': '2026-08-04T21:51:01.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1064717469372851', 'commentId': '1064717469372851', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzEwNjQ3MTc0NjkzNzI4NTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xMDY0NzE3NDY5MzcyODUx', 'date': '2026-08-13T11:44:18.000</t>
         </is>
       </c>
     </row>
@@ -3406,23 +3421,23 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Traigan la colección de Pokémon primera generación</t>
+          <t>A mi hijo, para encantarle esas, caquitas, como él le dice 😅</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-04T14:34:31.000Z</t>
+          <t>2026-08-07T06:03:05.000Z</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46238.60730324074</v>
+        <v>46241.2521412037</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>14:34:31</t>
+          <t>06:03:05</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -3439,7 +3454,7 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=1771499450700178', 'commentId': '1771499450700178', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NzE0OTk0NTA3MDAxNzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzcxNDk5NDUwNzAwMTc4', 'date': '2026-08-04T14:34:31.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=1993036815417987', 'commentId': '1993036815417987', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5OTMwMzY4MTU0MTc5ODc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTkzMDM2ODE1NDE3OTg3', 'date': '2026-08-07T06:03:05.000</t>
         </is>
       </c>
     </row>
@@ -3465,23 +3480,23 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Son muchos</t>
+          <t>Los niños persiguen colecciones de cualquier animal, animación o caricaturas pero no creo que sé desesperen en colecciónar emojis de mierda... De hecho mi hija dejo de tomar ése producto porque detesta ése masa con parecido a mierda</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-02T21:00:35.000Z</t>
+          <t>2026-08-06T01:08:17.000Z</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46236.87540509259</v>
+        <v>46240.04741898148</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>21:00:35</t>
+          <t>01:08:17</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3498,7 +3513,7 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=869709302677278', 'commentId': '869709302677278', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzg2OTcwOTMwMjY3NzI3OA==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml84Njk3MDkzMDI2NzcyNzg=', 'date': '2026-08-06T01:08:17.000Z'</t>
         </is>
       </c>
     </row>
@@ -3524,29 +3539,27 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Yo creo que el encargado no se hizo entender.
-Empleado: Que colección de Mochis sacamos ahora!
-Jefe: Cualquier mierda.</t>
+          <t>ya no saben que inventar alv</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-28T21:56:33.000Z</t>
+          <t>2026-08-05T23:13:06.000Z</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46231.91427083333</v>
+        <v>46239.96743055555</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>21:56:33</t>
+          <t>23:13:06</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3559,7 +3572,7 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02T5PxL8CwMwC1xqrgHkFvjr7RqATPbCxFLCJEjLDBtr1iTDJj1FmFHDPdMmmH6qBbl?comment_id=887158200755851', 'commentId': '887158200755851', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzg4NzE1ODIwMDc1NTg1MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml84ODcxNTgyMDA3NTU4NTE=', 'date': '2026-08-05T23:13:06.000Z'</t>
         </is>
       </c>
     </row>
@@ -3585,23 +3598,23 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
+          <t>Si traigan Pokémon pero en plástico duro no en Mochis q no son duraderos</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-18T01:02:17.000Z</t>
+          <t>2026-08-04T21:51:01.000Z</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46221.04325231481</v>
+        <v>46238.91042824074</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>46221</v>
+        <v>46238</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>01:02:17</t>
+          <t>21:51:01</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -3618,7 +3631,7 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=2717205488697179', 'commentId': '2717205488697179', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzI3MTcyMDU0ODg2OTcxNzk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yNzE3MjA1NDg4Njk3MTc5', 'date': '2026-08-04T21:51:01.000Z</t>
         </is>
       </c>
     </row>
@@ -3642,13 +3655,29 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Traigan la colección de Pokémon primera generación</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:34:31.000Z</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>46238.60730324074</v>
+      </c>
+      <c r="I61" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>14:34:31</t>
+        </is>
+      </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3658,16 +3687,16 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0Pcmk4X4bnNGD8gpjthFobYH7onh8eberWL3DP9vjB1hoE4buxTqSmQWZeCLGvDJil?comment_id=1771499450700178', 'commentId': '1771499450700178', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NzE0OTk0NTA3MDAxNzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzcxNDk5NDUwNzAwMTc4', 'date': '2026-08-04T14:34:31.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3676,34 +3705,34 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hola nuestros regalos está muy delicioso</t>
+          <t>Son muchos</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-16T13:13:12.000Z</t>
+          <t>2026-08-02T21:00:35.000Z</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46250.55083333333</v>
+        <v>46236.87540509259</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>46250</v>
+        <v>46236</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>13:13:12</t>
+          <t>21:00:35</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -3720,13 +3749,13 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=2473667986464388', 'commentId': '2473667986464388', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzI0NzM2Njc5ODY0NjQzODg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yNDczNjY3OTg2NDY0Mzg4', 'date': '2026-08-16T13:13:12.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0PJyDo1m8nGZ4GBCzD1CDm5Yv4sAWNGjrov9Xupv6GWk22XHgdFKFpHFefSVUEjwnl?comment_id=1753061509477915', 'commentId': '1753061509477915', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE3NTMwNjE1MDk0Nzc5MTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xNzUzMDYxNTA5NDc3OTE1', 'date': '2026-08-02T21:00:35.000Z</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3735,38 +3764,40 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Te amo yo voy yo favorito cómo está yo voy yo te amo mucho</t>
+          <t>Yo creo que el encargado no se hizo entender.
+Empleado: Que colección de Mochis sacamos ahora!
+Jefe: Cualquier mierda.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-16T13:13:12.000Z</t>
+          <t>2026-07-28T21:56:33.000Z</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46250.55083333333</v>
+        <v>46231.91427083333</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>46250</v>
+        <v>46231</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>13:13:12</t>
+          <t>21:56:33</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3779,13 +3810,13 @@
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1775962996878946', 'commentId': '1775962996878946', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE3NzU5NjI5OTY4Nzg5NDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNzc1OTYyOTk2ODc4OTQ2', 'date': '2026-08-16T13:13:12.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02TCvRJTvyGYP8v61YxyazJdsuX3wfaHneaDvaovRvn32UTCGRTQL4ddzth8RM47Yzl?comment_id=1983536282309777', 'commentId': '1983536282309777', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzE5ODM1MzYyODIzMDk3Nzc=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8xOTgzNTM2MjgyMzA5Nzc3', 'date': '2026-07-28T21:56:33.000</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3794,34 +3825,34 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hola está muy bueno este te digo te digo que yo te amo mi princesa favorito era como</t>
+          <t>Cómo dañaron la colección, queremos dinosaurios y animales marinos. Los bollos se los pueden meter por la cola.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-16T13:13:12.000Z</t>
+          <t>2026-07-18T01:02:17.000Z</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46250.55083333333</v>
+        <v>46221.04325231481</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>46250</v>
+        <v>46221</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>13:13:12</t>
+          <t>01:02:17</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -3838,13 +3869,13 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1322467810946455', 'commentId': '1322467810946455', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzEzMjI0Njc4MTA5NDY0NTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xMzIyNDY3ODEwOTQ2NDU1', 'date': '2026-08-16T13:13:12.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02SwdPMjsWu6CA7N2Dxq3GDHnoYMguU74SniAEG9qaHTjVX87E3VsaDZTGNC8SCEeul?comment_id=2000809543966891', 'commentId': '2000809543966891', 'id': 'Y29tbWVudDoxNDc4NjE3NTI0MzEwNDgyXzIwMDA4MDk1NDM5NjY4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYxNzUyNDMxMDQ4Ml8yMDAwODA5NTQzOTY2ODkx', 'date': '2026-07-18T01:02:17.000</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3853,36 +3884,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Con</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-08-16T13:13:12.000Z</t>
-        </is>
-      </c>
-      <c r="H65" s="1" t="n">
-        <v>46250.55083333333</v>
-      </c>
-      <c r="I65" s="1" t="n">
-        <v>46250</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>13:13:12</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>0</v>
       </c>
@@ -3894,12 +3909,12 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1753934642412589', 'commentId': '1753934642412589', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE3NTM5MzQ2NDI0MTI1ODk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNzUzOTM0NjQyNDEyNTg5', 'date': '2026-08-16T13:13:12.000</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3923,27 +3938,29 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>La basura que con sumen los aguebados jajaja</t>
+          <t>Ya perdiste la inspiración:(</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-18T02:24:12.000Z</t>
+          <t>2026-08-23T08:53:42.000Z</t>
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46221.10013888889</v>
-      </c>
-      <c r="I66" s="1" t="n">
-        <v>46221</v>
+        <v>46257.370625</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>46257</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>02:24:12</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+          <t>08:53:42</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3956,7 +3973,7 @@
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nD67i8rwKA8rM3CSo72unLuXUZnzQFERpyt6Gbdrz3yL79kqhaPY1XoxemM58Zcjl?comment_id=2195589671353576', 'commentId': '2195589671353576', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIxOTU1ODk2NzEzNTM1NzY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMTk1NTg5NjcxMzUzNTc2', 'date': '2026-08-23T08:53:42.000</t>
         </is>
       </c>
     </row>
@@ -3982,23 +3999,23 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
+          <t>Hola nuestros regalos está muy delicioso</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-18T00:09:32.000Z</t>
+          <t>2026-08-16T13:13:12.000Z</t>
         </is>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46221.00662037037</v>
+        <v>46250.55083333333</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>46221</v>
+        <v>46250</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>00:09:32</t>
+          <t>13:13:12</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4015,7 +4032,7 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=2473667986464388', 'commentId': '2473667986464388', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzI0NzM2Njc5ODY0NjQzODg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yNDczNjY3OTg2NDY0Mzg4', 'date': '2026-08-16T13:13:12.000</t>
         </is>
       </c>
     </row>
@@ -4041,23 +4058,23 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
+          <t>Te amo yo voy yo favorito cómo está yo voy yo te amo mucho</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-16T01:37:23.000Z</t>
+          <t>2026-08-16T13:13:12.000Z</t>
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46219.06762731481</v>
+        <v>46250.55083333333</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>46219</v>
+        <v>46250</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>01:37:23</t>
+          <t>13:13:12</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4074,7 +4091,7 @@
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1775962996878946', 'commentId': '1775962996878946', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE3NzU5NjI5OTY4Nzg5NDY=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNzc1OTYyOTk2ODc4OTQ2', 'date': '2026-08-16T13:13:12.000</t>
         </is>
       </c>
     </row>
@@ -4098,11 +4115,27 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Hola está muy bueno este te digo te digo que yo te amo mi princesa favorito era como</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-16T13:13:12.000Z</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>46250.55083333333</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>13:13:12</t>
+        </is>
+      </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
@@ -4114,16 +4147,16 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1322467810946455', 'commentId': '1322467810946455', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzEzMjI0Njc4MTA5NDY0NTU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xMzIyNDY3ODEwOTQ2NDU1', 'date': '2026-08-16T13:13:12.000</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4132,20 +4165,36 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Con</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-16T13:13:12.000Z</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="n">
+        <v>46250.55083333333</v>
+      </c>
+      <c r="I70" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>13:13:12</t>
+        </is>
+      </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
@@ -4157,16 +4206,16 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02nUG6eqchQaLTUZinFSPNfkAyzPGNn4XvmU4LLBoEB8H6ZAKQfZCfMbrbgsqAdfGol?comment_id=1753934642412589', 'commentId': '1753934642412589', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE3NTM5MzQ2NDI0MTI1ODk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNzUzOTM0NjQyNDEyNTg5', 'date': '2026-08-16T13:13:12.000</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4175,20 +4224,36 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>La basura que con sumen los aguebados jajaja</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>46221.10013888889</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>02:24:12</t>
+        </is>
+      </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
@@ -4200,16 +4265,16 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1570496154770550', 'commentId': '1570496154770550', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NzA0OTYxNTQ3NzA1NTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTcwNDk2MTU0NzcwNTUw', 'date': '2026-07-18T02:24:12.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4218,34 +4283,34 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Que gonorrea</t>
+          <t>Esos emochis me parecen un poco peligrosos ya que los niños lo pueden ingerir deberían cambiar para innovar.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-04T11:01:26.000Z</t>
+          <t>2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>46238.45932870371</v>
+        <v>46221.00662037037</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>46238</v>
+        <v>46221</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>11:01:26</t>
+          <t>00:09:32</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4262,13 +4327,13 @@
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=2061225511435404', 'commentId': '2061225511435404', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzIwNjEyMjU1MTE0MzU0MDQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8yMDYxMjI1NTExNDM1NDA0', 'date': '2026-07-18T00:09:32.000Z</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4277,38 +4342,38 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Aghevado</t>
+          <t>Hfeertrt5ŕf fvrŕ4cjj</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-08-02T23:37:51.000Z</t>
+          <t>2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>46236.98461805555</v>
+        <v>46219.06762731481</v>
       </c>
       <c r="I73" s="1" t="n">
-        <v>46236</v>
+        <v>46219</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>23:37:51</t>
+          <t>01:37:23</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4321,13 +4386,13 @@
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0iV3pVnMT6VPyis1ayuqAo6SWPdgFRkmDNxrtTmqSCYkgiGzhmD56aBwEjJw2aPJ4l?comment_id=1554955609342819', 'commentId': '1554955609342819', 'id': 'Y29tbWVudDoxNDgxNTMzMDM3MzUyMjY0XzE1NTQ5NTU2MDkzNDI4MTk=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUzMzAzNzM1MjI2NF8xNTU0OTU1NjA5MzQyODE5', 'date': '2026-07-16T01:37:23.000Z</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4336,36 +4401,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Si también yo todo una bb y le yebo debes en cuando</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2026-08-02T03:54:11.000Z</t>
-        </is>
-      </c>
-      <c r="H74" s="1" t="n">
-        <v>46236.16262731481</v>
-      </c>
-      <c r="I74" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>03:54:11</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
         <v>0</v>
       </c>
@@ -4377,16 +4426,16 @@
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
-        </is>
-      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4395,38 +4444,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Alanissofia</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2026-08-02T00:21:49.000Z</t>
-        </is>
-      </c>
-      <c r="H75" s="1" t="n">
-        <v>46236.01515046296</v>
-      </c>
-      <c r="I75" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>00:21:49</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4436,16 +4469,16 @@
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
-        </is>
-      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4454,36 +4487,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Mensajes subliminales para aceptar la violencia ojo</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2026-07-29T20:28:55.000Z</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="n">
-        <v>46232.85341435186</v>
-      </c>
-      <c r="I76" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>20:28:55</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>0</v>
       </c>
@@ -4495,12 +4512,12 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
-        </is>
-      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4522,13 +4539,31 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Pokemon por favor si  yogo yogo</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:34:18.000Z</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>46257.19048611111</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>46257</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>04:34:18</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4538,16 +4573,16 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BoVWHYx5NttQaiq19egoS9yiUoHBY9hoaSHZbvef5qF1K16WJQyeqZQFeUuXRywUl?comment_id=1617206456420442', 'commentId': '1617206456420442', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE2MTcyMDY0NTY0MjA0NDI=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNjE3MjA2NDU2NDIwNDQy', 'date': '2026-08-23T04:34:18.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4556,34 +4591,34 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Otra vez 🤔 fracaso total 🤣🤣🤣</t>
+          <t>Que gonorrea</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-08-13T01:57:58.000Z</t>
+          <t>2026-08-04T11:01:26.000Z</t>
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46247.0819212963</v>
+        <v>46238.45932870371</v>
       </c>
       <c r="I78" s="1" t="n">
-        <v>46247</v>
+        <v>46238</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>01:57:58</t>
+          <t>11:01:26</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -4600,13 +4635,13 @@
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0zczcVQYKvjt1AjhEfswpqNUvaExrsMHdvMZCH6eBfdrdqebuqVyYaQQG1T9G5hUml?comment_id=1752018369330843', 'commentId': '1752018369330843', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE3NTIwMTgzNjkzMzA4NDM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNzUyMDE4MzY5MzMwODQz', 'date': '2026-08-13T01:57:58.000Z</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07pHE8Vgq4khHHG9EXUKCqaEFg2u7FecWpdKf2WzPA6PYFrgEdRnFSsNqLEvHJeEyl?comment_id=1071006878605975', 'commentId': '1071006878605975', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNzEwMDY4Nzg2MDU5NzU=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDcxMDA2ODc4NjA1OTc1', 'date': '2026-08-04T11:01:26.000Z'</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4615,39 +4650,38 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Que mala calidad ,los ojos no duran ni 5 minutos 
-Vuelvan à las figuras de antes</t>
+          <t>Aghevado</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-05T02:25:32.000Z</t>
+          <t>2026-08-02T23:37:51.000Z</t>
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46239.10106481481</v>
+        <v>46236.98461805555</v>
       </c>
       <c r="I79" s="1" t="n">
-        <v>46239</v>
+        <v>46236</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>02:25:32</t>
+          <t>23:37:51</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4660,13 +4694,13 @@
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0345VmkzNyE8NyxycLLvKZBHyGjZ9PXZcabasRdHNz1iifGzbtXGx5e3NxwcbrhjdTl?comment_id=1562612211978101', 'commentId': '1562612211978101', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE1NjI2MTIyMTE5NzgxMDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNTYyNjEyMjExOTc4MTAx', 'date': '2026-08-05T02:25:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BqswcJtPjiGWEXDsqisjaKBBM6PVP7xNuuqLPGDXkQVKZjfn2ZkenUtbxEGjUSwLl?comment_id=1356280102712938', 'commentId': '1356280102712938', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEzNTYyODAxMDI3MTI5Mzg=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMzU2MjgwMTAyNzEyOTM4', 'date': '2026-08-02T23:37:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4675,34 +4709,34 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Por que los nuevos se parecen a la 💩</t>
+          <t>Si también yo todo una bb y le yebo debes en cuando</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-24T07:43:32.000Z</t>
+          <t>2026-08-02T03:54:11.000Z</t>
         </is>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46227.32189814815</v>
+        <v>46236.16262731481</v>
       </c>
       <c r="I80" s="1" t="n">
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>03:54:11</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -4719,13 +4753,13 @@
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1901614314502401', 'commentId': '1901614314502401', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE5MDE2MTQzMTQ1MDI0MDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xOTAxNjE0MzE0NTAyNDAx', 'date': '2026-08-02T03:54:11.000Z'</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4734,38 +4768,38 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
+          <t>Alanissofia</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-23T22:50:34.000Z</t>
+          <t>2026-08-02T00:21:49.000Z</t>
         </is>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46226.95178240741</v>
+        <v>46236.01515046296</v>
       </c>
       <c r="I81" s="1" t="n">
-        <v>46226</v>
+        <v>46236</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>22:50:34</t>
+          <t>00:21:49</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4778,13 +4812,13 @@
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07zSERdxZtFiwp44hT264ChLpDMbeLo2FedWxPvd7G7HaErjGD96FQc14ALQivo4Ml?comment_id=1593169822152364', 'commentId': '1593169822152364', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzE1OTMxNjk4MjIxNTIzNjQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xNTkzMTY5ODIyMTUyMzY0', 'date': '2026-08-02T00:21:49.000Z'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -4793,20 +4827,36 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mensajes subliminales para aceptar la violencia ojo</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>20:28:55</t>
+        </is>
+      </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
@@ -4818,16 +4868,16 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02BiERdwrfZCxzmPjPCVVfzaBcKQVrGatcRBoCUjL51rzshpcuBZKqhq9jsPGMarsol?comment_id=1042387978297774', 'commentId': '1042387978297774', 'id': 'Y29tbWVudDoxNDc4NjA3Njc0MzExNDY3XzEwNDIzODc5NzgyOTc3NzQ=', 'feedbackId': 'ZmVlZGJhY2s6MTQ3ODYwNzY3NDMxMTQ2N18xMDQyMzg3OTc4Mjk3Nzc0', 'date': '2026-07-29T20:28:55.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -4836,12 +4886,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4870,7 +4920,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4879,20 +4929,36 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Otra vez 🤔 fracaso total 🤣🤣🤣</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-08-13T01:57:58.000Z</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>46247.0819212963</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>01:57:58</t>
+        </is>
+      </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
@@ -4904,38 +4970,55 @@
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0zczcVQYKvjt1AjhEfswpqNUvaExrsMHdvMZCH6eBfdrdqebuqVyYaQQG1T9G5hUml?comment_id=1752018369330843', 'commentId': '1752018369330843', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE3NTIwMTgzNjkzMzA4NDM=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNzUyMDE4MzY5MzMwODQz', 'date': '2026-08-13T01:57:58.000Z</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Que mala calidad ,los ojos no duran ni 5 minutos 
+Vuelvan à las figuras de antes</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-08-05T02:25:32.000Z</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>46239.10106481481</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>02:25:32</t>
+        </is>
+      </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
@@ -4947,56 +5030,52 @@
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid0345VmkzNyE8NyxycLLvKZBHyGjZ9PXZcabasRdHNz1iifGzbtXGx5e3NxwcbrhjdTl?comment_id=1562612211978101', 'commentId': '1562612211978101', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE1NjI2MTIyMTE5NzgxMDE=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNTYyNjEyMjExOTc4MTAx', 'date': '2026-08-05T02:25:32.000</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>jholman.romero</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Coleccion de kgadas 🤣</t>
+          <t>Por que los nuevos se parecen a la 💩</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-08-19T16:57:42.000Z</t>
+          <t>2026-07-24T07:43:32.000Z</t>
         </is>
       </c>
       <c r="H86" s="1" t="n">
-        <v>46253.70673611111</v>
+        <v>46227.32189814815</v>
       </c>
       <c r="I86" s="1" t="n">
-        <v>46253</v>
+        <v>46227</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>16:57:42</t>
+          <t>07:43:32</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -5009,65 +5088,57 @@
         <v>0</v>
       </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>https://instagram.com/jholman.romero</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18113336536999344', 'id': '18113336536999344', 'text': 'Coleccion de kgadas 🤣', 'ownerUsername': 'jholman.romero', 'ownerProfilePicUrl': 'https://instagram.frtm1-3.fna.fbcdn.net/v/t51.82787-19/772713138_18450874516140269_5868174430896753472_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=instagram.frtm1-3.fna.fbcdn.net&amp;_nc_cat=105&amp;</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=1623593502720010', 'commentId': '1623593502720010', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzE2MjM1OTM1MDI3MjAwMTA=', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8xNjIzNTkzNTAyNzIwMDEw', 'date': '2026-07-24T07:43:32.000</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>cristian.oj25</t>
-        </is>
-      </c>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tu antes eras divertido</t>
+          <t>Yogoyogo de mierdita tiene Loka a mi hija x conseguirlos</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-08-06T06:06:31.000Z</t>
+          <t>2026-07-23T22:50:34.000Z</t>
         </is>
       </c>
       <c r="H87" s="1" t="n">
-        <v>46240.25452546297</v>
+        <v>46226.95178240741</v>
       </c>
       <c r="I87" s="1" t="n">
-        <v>46240</v>
+        <v>46226</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>06:06:31</t>
+          <t>22:50:34</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -5076,35 +5147,31 @@
         <v>0</v>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>https://instagram.com/cristian.oj25</t>
-        </is>
-      </c>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18154436263497089', 'id': '18154436263497089', 'text': 'Tu antes eras divertido', 'ownerUsername': 'cristian.oj25', 'ownerProfilePicUrl': 'https://scontent-mad2-1.cdninstagram.com/v/t51.2885-19/473706151_2383626751975725_6503272042622682934_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4zMjAuYzIifQ&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=109&amp;</t>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid034AWkQYrzW5sjt4mHDW6coXCFscK6TAVtoMwopn2yGLAWACzz9wPAfC1Pbw75tur8l?comment_id=27678974671752229', 'commentId': '27678974671752229', 'id': 'Y29tbWVudDoxNDgxNTE5MjYwNjg2OTc1XzI3Njc4OTc0NjcxNzUyMjI5', 'feedbackId': 'ZmVlZGJhY2s6MTQ4MTUxOTI2MDY4Njk3NV8yNzY3ODk3NDY3MTc1MjIyOQ==', 'date': '2026-07-23T22:50:</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -5133,21 +5200,21 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -5176,21 +5243,21 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -5219,7 +5286,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5228,12 +5295,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -5262,7 +5329,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5271,20 +5338,40 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>jholman.romero</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Coleccion de kgadas 🤣</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:57:42.000Z</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>46253.70673611111</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>16:57:42</t>
+        </is>
+      </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
@@ -5295,17 +5382,21 @@
         <v>0</v>
       </c>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jholman.romero</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18113336536999344', 'id': '18113336536999344', 'text': 'Coleccion de kgadas 🤣', 'ownerUsername': 'jholman.romero', 'ownerProfilePicUrl': 'https://instagram.frtm1-3.fna.fbcdn.net/v/t51.82787-19/772713138_18450874516140269_5868174430896753472_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=instagram.frtm1-3.fna.fbcdn.net&amp;_nc_cat=105&amp;</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5314,22 +5405,42 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>cristian.oj25</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tu antes eras divertido</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-08-06T06:06:31.000Z</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>46240.25452546297</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>06:06:31</t>
+        </is>
+      </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -5338,17 +5449,21 @@
         <v>0</v>
       </c>
       <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>https://instagram.com/cristian.oj25</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/', 'commentUrl': 'https://www.instagram.com/p/Dax0GBqgVfJ/c/18154436263497089', 'id': '18154436263497089', 'text': 'Tu antes eras divertido', 'ownerUsername': 'cristian.oj25', 'ownerProfilePicUrl': 'https://scontent-mad2-1.cdninstagram.com/v/t51.2885-19/473706151_2383626751975725_6503272042622682934_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4zMjAuYzIifQ&amp;_nc_ht=scontent-mad2-1.cdninstagram.com&amp;_nc_cat=109&amp;</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5357,12 +5472,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5391,7 +5506,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5400,12 +5515,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -5434,7 +5549,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5443,40 +5558,20 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Muy mal nombre la verdad :vv</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026-07-26T10:28:53.000Z</t>
-        </is>
-      </c>
-      <c r="H96" s="1" t="n">
-        <v>46229.43672453704</v>
-      </c>
-      <c r="I96" s="1" t="n">
-        <v>46229</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>10:28:53</t>
-        </is>
-      </c>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="n">
         <v>0</v>
       </c>
@@ -5487,21 +5582,17 @@
         <v>0</v>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>https://instagram.com/sleepy_dunez</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
-        </is>
-      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5510,12 +5601,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -5544,7 +5635,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5553,20 +5644,40 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>j._.r2006</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mierdochis</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-08-25T04:32:28.000Z</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>46259.18921296296</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>04:32:28</t>
+        </is>
+      </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
@@ -5577,17 +5688,21 @@
         <v>0</v>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>https://instagram.com/j._.r2006</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DaxyhZDAdzK/', 'commentUrl': 'https://www.instagram.com/p/DaxyhZDAdzK/c/18111210386142739', 'id': '18111210386142739', 'text': 'Mierdochis', 'ownerUsername': 'j._.r2006', 'ownerProfilePicUrl': 'https://instagram.fcyw1-1.fna.fbcdn.net/v/t51.82787-19/773981524_18108689246334885_7169791312420405640_n.jpg?stp=dst-jpg_s150x150_tt6&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InByb2ZpbGVfcGljLmRqYW5nby4xMDgwLmMyIn0&amp;_nc_ht=instagram.fcyw1-1.fna.fbcdn.net&amp;_nc_cat=109&amp;_nc_oc=Q6cZ2gEif</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5596,12 +5711,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -5628,6 +5743,2005 @@
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>39</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>40</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>41</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>42</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Muy mal nombre la verdad :vv</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-07-26T10:28:53.000Z</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>10:28:53</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sleepy_dunez</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/', 'commentUrl': 'https://www.instagram.com/p/Dax0ftQgN6m/c/18150829300509872', 'id': '18150829300509872', 'text': 'Muy mal nombre la verdad :vv', 'ownerUsername': 'sleepy_dunez', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/726373129_17888033775561289_5001866020940776711_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=110&amp;ig_cache_key=GAmTSytJKuxqEo0-AAeFRSClMmpFbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=ey</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>42</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>43</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>44</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>post_number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>post_url</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Total_Comentarios</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total_Likes</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Primera_Extraccion</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ultima_Extraccion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/3261599530668110/</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5yxYgAy5c/</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46210.59957175926</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>46211.58980324074</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>46220.97578703704</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>46259.67501157407</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>46217.89942129629</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>46243.94265046297</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>46221.04325231481</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>46255.09995370371</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46219.06762731481</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>46257.370625</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>46232.85341435186</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46257.19048611111</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>46226.95178240741</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46247.0819212963</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0GBqgVfJ/</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>46240.25452546297</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>46253.70673611111</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxyhZDAdzK/</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>46259.18921296296</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>46259.18921296296</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dax0ftQgN6m/</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+      <c r="G43" s="1" t="n">
+        <v>46229.43672453704</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Total_Posts</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Total_Comentarios</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Promedio_Likes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total_Likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02wii1P1pD2H7gkGwQfcYVVDWuGRYjto2YEykU9x3EViVfR74LZVBZjDGKtTGUNs5l</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0KW1D1SQ7N3wkb6y3CghuTp8cCTqL7spikmcNds9w8dXUWbZoqf4PGtW1TCFC4mBdl</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0HdzfymKuNH5WHHiBr2w9GheCM5tjxp9SDPbiWX83wFUVFAQbj1A5fzaiB5BgrP34l</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jqKsZHCWqyFzLmcCQ1DVBQKxhACNHVh8NrXTvpiWeBjuEwYAumJXpougMVRoKX31l</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06rYqXZEpGhYe2vcmZ5WfevUVLR1AhYePytnJmqt6kk525bMTpDjhDwoJpgpkyWrWl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/3261599530668110/</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/1EVoU9fDD6/</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/18vjmR9EbP/</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/p/19G6LM1Pof/</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/share/v/1JB8tmKYtm/</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>total_attempts</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>successful</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>no_comments</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>invalid_comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -20,11 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -55,10 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1541,7 +1538,7 @@
       <c r="H24" s="1" t="n">
         <v>46259.67501157407</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="J24" t="inlineStr">
@@ -1549,10 +1546,8 @@
           <t>16:12:01</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K24" t="n">
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1602,7 +1597,7 @@
       <c r="H25" s="1" t="n">
         <v>46258.13662037037</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I25" s="1" t="n">
         <v>46258</v>
       </c>
       <c r="J25" t="inlineStr">
@@ -1610,10 +1605,8 @@
           <t>03:16:44</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K25" t="n">
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1663,7 +1656,7 @@
       <c r="H26" s="1" t="n">
         <v>46257.81375</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="1" t="n">
         <v>46257</v>
       </c>
       <c r="J26" t="inlineStr">
@@ -1671,10 +1664,8 @@
           <t>19:31:48</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K26" t="n">
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3253,7 +3244,7 @@
       <c r="H54" s="1" t="n">
         <v>46255.09995370371</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="J54" t="inlineStr">
@@ -3261,10 +3252,8 @@
           <t>02:23:56</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K54" t="n">
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3949,7 +3938,7 @@
       <c r="H66" s="1" t="n">
         <v>46257.370625</v>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I66" s="1" t="n">
         <v>46257</v>
       </c>
       <c r="J66" t="inlineStr">
@@ -3957,10 +3946,8 @@
           <t>08:53:42</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K66" t="n">
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4552,7 +4539,7 @@
       <c r="H77" s="1" t="n">
         <v>46257.19048611111</v>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="I77" s="1" t="n">
         <v>46257</v>
       </c>
       <c r="J77" t="inlineStr">
@@ -4560,10 +4547,8 @@
           <t>04:34:18</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="K77" t="n">
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5670,7 +5655,7 @@
       <c r="H98" s="1" t="n">
         <v>46259.18921296296</v>
       </c>
-      <c r="I98" s="2" t="n">
+      <c r="I98" s="1" t="n">
         <v>46259</v>
       </c>
       <c r="J98" t="inlineStr">
@@ -7261,7 +7246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7399,7 +7384,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02awSRn7qMHiopGBURJWVj5Yqv6Kxy5dgs7RKPfdZSLYSd2ZUZkJv52cwE582X2XyFl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7411,7 +7396,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0diXSKWcBuTriKjD7Nwt6JVvYPUCCtYhUPBXacCtRb66LmEM7VnPzk5mNx4SPFu81l</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7423,7 +7408,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0u3H29b1191LidQ6R4ScnVbymeypHNjdJZgFg9d7fSGNsjJzHXvKF8W1yBTzet227l</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7435,7 +7420,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02RJW4as6otnHmCuYRMm2c5Uh2KDJvcJykcUsjmRwGtE3BEJobZjT8PosVhhqKGQvYl</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7447,7 +7432,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02jvvAfrhCFmzTnxK1pvNmh15Y8qThsqiWPocQ9dUo3kETV4HhCXc3ZffrAaq4gEHrl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7459,7 +7444,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02c5QGzXhE2N8V1K1dYhrycRLWmoqMyPgLhkoUWws3WrATKMY3QeVVcgeSE9mTM73Ll</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7471,7 +7456,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0ZQYTeNNy2eTtEqRUWUG3sno85TQAQEpp1UC65toR11BoHe3VFGVtckUw4Sf7bAVFl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7483,7 +7468,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid02MxKsxXBXFoAXeZcMJQ3Qn8BrrisRTgMzVgtbyNssSZf4nLr47uJCMFKPzs8wWYGhl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7495,7 +7480,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0jxSvw9oJXMG8A9eNrYVsqbDjjpFB4wAe6hpkFkKpK5TzU6AHetEfBbNHp7m6gHLil</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7507,7 +7492,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid029TVtHR1KfaW4AsBqfonhJ1VHSfG32B4BmVrYEXwaXxRBm6npftXSEnoxPPs5zpEYl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7519,7 +7504,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid0LSCGwRefL4RtjMGDw8x4sPBjcpUvG5Nb7sspUQA3u2FxNKfKPce62zJbG84DLiNrl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7531,7 +7516,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
+          <t>https://www.facebook.com/100064867445065/posts/pfbid06cvKsDX83RU1JegqcrpMTftA37dFcZNmD3rHssE245K5AzJfVim7LbydRbMvPedgl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7543,7 +7528,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
+          <t>https://www.instagram.com/p/DZNxPDAALy4/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7555,7 +7540,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
+          <t>https://www.instagram.com/p/DZNxHkkgASI/</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7567,7 +7552,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
+          <t>https://www.instagram.com/p/DZMS8j3gLwc/</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7579,7 +7564,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
+          <t>https://www.instagram.com/p/DZMSywUgClm/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7591,7 +7576,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
+          <t>https://www.instagram.com/p/DZLkuhcgMiD/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7603,7 +7588,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+          <t>https://www.instagram.com/p/DZgJjAmgNkB/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7615,7 +7600,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+          <t>https://www.instagram.com/p/DZ5ypteA0CO/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7627,7 +7612,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+          <t>https://www.instagram.com/p/DZ5t8kSAvF3/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7639,7 +7624,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+          <t>https://www.instagram.com/p/DZ5zHVwAbLS/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7651,7 +7636,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+          <t>https://www.instagram.com/p/Dao8BvHgwPO/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7663,7 +7648,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+          <t>https://www.instagram.com/p/Dao9WjmA7W6/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7675,10 +7660,82 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/p/DaxwTQ4gyKQ/</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_lUkAI8z/</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DapAo_QgLPK/</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DaxzJ8jgGVl/</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao-Ke_AEaE/</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dao_BRHA1YQ/</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FAILED_ALL_ATTEMPTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/p/Daxx_DygJuZ/</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>FAILED_ALL_ATTEMPTS</t>
         </is>
@@ -7730,16 +7787,16 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
